--- a/output/version3/test/10-5/MARL/IL/RL-RL (+comm+it)/(RL+RL) test results.xlsx
+++ b/output/version3/test/10-5/MARL/IL/RL-RL (+comm+it)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
+        <v>436</v>
+      </c>
+      <c r="C2" t="n">
+        <v>420</v>
+      </c>
+      <c r="D2" t="n">
+        <v>446</v>
+      </c>
+      <c r="E2" t="n">
+        <v>485</v>
+      </c>
+      <c r="F2" t="n">
+        <v>415</v>
+      </c>
+      <c r="G2" t="n">
+        <v>473</v>
+      </c>
+      <c r="H2" t="n">
+        <v>429</v>
+      </c>
+      <c r="I2" t="n">
         <v>464</v>
       </c>
-      <c r="C2" t="n">
-        <v>450</v>
-      </c>
-      <c r="D2" t="n">
-        <v>495</v>
-      </c>
-      <c r="E2" t="n">
-        <v>497</v>
-      </c>
-      <c r="F2" t="n">
-        <v>446</v>
-      </c>
-      <c r="G2" t="n">
-        <v>522</v>
-      </c>
-      <c r="H2" t="n">
-        <v>495</v>
-      </c>
-      <c r="I2" t="n">
-        <v>481</v>
-      </c>
       <c r="J2" t="n">
-        <v>413</v>
+        <v>508</v>
       </c>
       <c r="K2" t="n">
-        <v>474</v>
+        <v>437</v>
       </c>
       <c r="L2" t="n">
-        <v>473.7</v>
+        <v>451.3</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>487</v>
+        <v>445</v>
       </c>
       <c r="C3" t="n">
-        <v>532</v>
+        <v>484</v>
       </c>
       <c r="D3" t="n">
-        <v>540</v>
+        <v>490</v>
       </c>
       <c r="E3" t="n">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="F3" t="n">
-        <v>580</v>
+        <v>502</v>
       </c>
       <c r="G3" t="n">
-        <v>456</v>
+        <v>479</v>
       </c>
       <c r="H3" t="n">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="I3" t="n">
-        <v>579</v>
+        <v>530</v>
       </c>
       <c r="J3" t="n">
-        <v>540</v>
+        <v>524</v>
       </c>
       <c r="K3" t="n">
-        <v>468</v>
+        <v>562</v>
       </c>
       <c r="L3" t="n">
-        <v>524.1</v>
+        <v>505.6</v>
       </c>
     </row>
     <row r="4">
@@ -547,34 +547,34 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>452</v>
+        <v>519</v>
       </c>
       <c r="C4" t="n">
-        <v>524</v>
+        <v>598</v>
       </c>
       <c r="D4" t="n">
-        <v>538</v>
+        <v>459</v>
       </c>
       <c r="E4" t="n">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="F4" t="n">
-        <v>588</v>
+        <v>485</v>
       </c>
       <c r="G4" t="n">
-        <v>545</v>
+        <v>505</v>
       </c>
       <c r="H4" t="n">
-        <v>481</v>
+        <v>557</v>
       </c>
       <c r="I4" t="n">
-        <v>503</v>
+        <v>486</v>
       </c>
       <c r="J4" t="n">
-        <v>524</v>
+        <v>473</v>
       </c>
       <c r="K4" t="n">
-        <v>471</v>
+        <v>550</v>
       </c>
       <c r="L4" t="n">
         <v>512</v>
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>498</v>
+        <v>469</v>
       </c>
       <c r="C5" t="n">
-        <v>428</v>
+        <v>474</v>
       </c>
       <c r="D5" t="n">
-        <v>579</v>
+        <v>524</v>
       </c>
       <c r="E5" t="n">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="F5" t="n">
+        <v>551</v>
+      </c>
+      <c r="G5" t="n">
+        <v>512</v>
+      </c>
+      <c r="H5" t="n">
         <v>482</v>
       </c>
-      <c r="G5" t="n">
-        <v>491</v>
-      </c>
-      <c r="H5" t="n">
-        <v>523</v>
-      </c>
       <c r="I5" t="n">
-        <v>488</v>
+        <v>549</v>
       </c>
       <c r="J5" t="n">
-        <v>470</v>
+        <v>554</v>
       </c>
       <c r="K5" t="n">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="L5" t="n">
-        <v>495.1</v>
+        <v>508.1</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>450</v>
+        <v>492</v>
       </c>
       <c r="C6" t="n">
-        <v>462</v>
+        <v>496</v>
       </c>
       <c r="D6" t="n">
-        <v>434</v>
+        <v>477</v>
       </c>
       <c r="E6" t="n">
-        <v>494</v>
+        <v>456</v>
       </c>
       <c r="F6" t="n">
-        <v>515</v>
+        <v>427</v>
       </c>
       <c r="G6" t="n">
-        <v>514</v>
+        <v>467</v>
       </c>
       <c r="H6" t="n">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="I6" t="n">
-        <v>416</v>
+        <v>452</v>
       </c>
       <c r="J6" t="n">
-        <v>429</v>
+        <v>543</v>
       </c>
       <c r="K6" t="n">
-        <v>440</v>
+        <v>475</v>
       </c>
       <c r="L6" t="n">
-        <v>461.3</v>
+        <v>473.3</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>463</v>
+        <v>392</v>
       </c>
       <c r="C7" t="n">
-        <v>484</v>
+        <v>444</v>
       </c>
       <c r="D7" t="n">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="E7" t="n">
-        <v>475</v>
+        <v>456</v>
       </c>
       <c r="F7" t="n">
-        <v>438</v>
+        <v>498</v>
       </c>
       <c r="G7" t="n">
-        <v>408</v>
+        <v>460</v>
       </c>
       <c r="H7" t="n">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="I7" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J7" t="n">
-        <v>511</v>
+        <v>528</v>
       </c>
       <c r="K7" t="n">
-        <v>441</v>
+        <v>467</v>
       </c>
       <c r="L7" t="n">
-        <v>457.1</v>
+        <v>460.7</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>469</v>
+        <v>504</v>
       </c>
       <c r="C8" t="n">
-        <v>540</v>
+        <v>490</v>
       </c>
       <c r="D8" t="n">
-        <v>545</v>
+        <v>493</v>
       </c>
       <c r="E8" t="n">
-        <v>551</v>
+        <v>473</v>
       </c>
       <c r="F8" t="n">
-        <v>535</v>
+        <v>472</v>
       </c>
       <c r="G8" t="n">
-        <v>505</v>
+        <v>557</v>
       </c>
       <c r="H8" t="n">
-        <v>544</v>
+        <v>479</v>
       </c>
       <c r="I8" t="n">
-        <v>558</v>
+        <v>534</v>
       </c>
       <c r="J8" t="n">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="K8" t="n">
-        <v>471</v>
+        <v>542</v>
       </c>
       <c r="L8" t="n">
-        <v>517.7</v>
+        <v>501.2</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>499</v>
+        <v>454</v>
       </c>
       <c r="C9" t="n">
-        <v>509</v>
+        <v>447</v>
       </c>
       <c r="D9" t="n">
-        <v>441</v>
+        <v>424</v>
       </c>
       <c r="E9" t="n">
-        <v>523</v>
+        <v>479</v>
       </c>
       <c r="F9" t="n">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="G9" t="n">
-        <v>481</v>
+        <v>465</v>
       </c>
       <c r="H9" t="n">
-        <v>440</v>
+        <v>474</v>
       </c>
       <c r="I9" t="n">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="J9" t="n">
+        <v>479</v>
+      </c>
+      <c r="K9" t="n">
         <v>434</v>
       </c>
-      <c r="K9" t="n">
-        <v>492</v>
-      </c>
       <c r="L9" t="n">
-        <v>473.8</v>
+        <v>455.2</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>534</v>
+        <v>436</v>
       </c>
       <c r="C10" t="n">
+        <v>490</v>
+      </c>
+      <c r="D10" t="n">
+        <v>465</v>
+      </c>
+      <c r="E10" t="n">
         <v>483</v>
       </c>
-      <c r="D10" t="n">
-        <v>502</v>
-      </c>
-      <c r="E10" t="n">
-        <v>514</v>
-      </c>
       <c r="F10" t="n">
-        <v>500</v>
+        <v>446</v>
       </c>
       <c r="G10" t="n">
-        <v>522</v>
+        <v>457</v>
       </c>
       <c r="H10" t="n">
-        <v>479</v>
+        <v>556</v>
       </c>
       <c r="I10" t="n">
-        <v>476</v>
+        <v>527</v>
       </c>
       <c r="J10" t="n">
-        <v>519</v>
+        <v>565</v>
       </c>
       <c r="K10" t="n">
-        <v>541</v>
+        <v>515</v>
       </c>
       <c r="L10" t="n">
-        <v>507</v>
+        <v>494</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>479</v>
+        <v>400</v>
       </c>
       <c r="C11" t="n">
-        <v>455</v>
+        <v>377</v>
       </c>
       <c r="D11" t="n">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="E11" t="n">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="F11" t="n">
-        <v>397</v>
+        <v>463</v>
       </c>
       <c r="G11" t="n">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="H11" t="n">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="I11" t="n">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="J11" t="n">
-        <v>454</v>
+        <v>481</v>
       </c>
       <c r="K11" t="n">
-        <v>435</v>
+        <v>461</v>
       </c>
       <c r="L11" t="n">
-        <v>444.8</v>
+        <v>436</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="C12" t="n">
-        <v>535</v>
+        <v>524</v>
       </c>
       <c r="D12" t="n">
-        <v>520</v>
+        <v>560</v>
       </c>
       <c r="E12" t="n">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="F12" t="n">
-        <v>489</v>
+        <v>517</v>
       </c>
       <c r="G12" t="n">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="H12" t="n">
-        <v>588</v>
+        <v>562</v>
       </c>
       <c r="I12" t="n">
-        <v>528</v>
+        <v>487</v>
       </c>
       <c r="J12" t="n">
-        <v>545</v>
+        <v>585</v>
       </c>
       <c r="K12" t="n">
-        <v>506</v>
+        <v>477</v>
       </c>
       <c r="L12" t="n">
-        <v>530</v>
+        <v>529.3</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>499</v>
+        <v>544</v>
       </c>
       <c r="C13" t="n">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D13" t="n">
-        <v>608</v>
+        <v>463</v>
       </c>
       <c r="E13" t="n">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F13" t="n">
-        <v>462</v>
+        <v>562</v>
       </c>
       <c r="G13" t="n">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="H13" t="n">
-        <v>477</v>
+        <v>532</v>
       </c>
       <c r="I13" t="n">
-        <v>584</v>
+        <v>542</v>
       </c>
       <c r="J13" t="n">
-        <v>503</v>
+        <v>530</v>
       </c>
       <c r="K13" t="n">
-        <v>445</v>
+        <v>519</v>
       </c>
       <c r="L13" t="n">
-        <v>521.1</v>
+        <v>532.2</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>531</v>
+        <v>502</v>
       </c>
       <c r="C14" t="n">
-        <v>596</v>
+        <v>534</v>
       </c>
       <c r="D14" t="n">
-        <v>579</v>
+        <v>568</v>
       </c>
       <c r="E14" t="n">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="F14" t="n">
-        <v>539</v>
+        <v>564</v>
       </c>
       <c r="G14" t="n">
-        <v>547</v>
+        <v>507</v>
       </c>
       <c r="H14" t="n">
-        <v>491</v>
+        <v>525</v>
       </c>
       <c r="I14" t="n">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="J14" t="n">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="K14" t="n">
-        <v>584</v>
+        <v>498</v>
       </c>
       <c r="L14" t="n">
-        <v>547.8</v>
+        <v>535.4</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="C15" t="n">
         <v>460</v>
       </c>
       <c r="D15" t="n">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="E15" t="n">
-        <v>472</v>
+        <v>419</v>
       </c>
       <c r="F15" t="n">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="G15" t="n">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="H15" t="n">
-        <v>486</v>
+        <v>519</v>
       </c>
       <c r="I15" t="n">
-        <v>421</v>
+        <v>450</v>
       </c>
       <c r="J15" t="n">
-        <v>467</v>
+        <v>444</v>
       </c>
       <c r="K15" t="n">
-        <v>441</v>
+        <v>487</v>
       </c>
       <c r="L15" t="n">
-        <v>458.3</v>
+        <v>462.8</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>470</v>
+        <v>445</v>
       </c>
       <c r="C16" t="n">
-        <v>521</v>
+        <v>456</v>
       </c>
       <c r="D16" t="n">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="E16" t="n">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="F16" t="n">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="G16" t="n">
-        <v>488</v>
+        <v>443</v>
       </c>
       <c r="H16" t="n">
-        <v>543</v>
+        <v>506</v>
       </c>
       <c r="I16" t="n">
-        <v>547</v>
+        <v>461</v>
       </c>
       <c r="J16" t="n">
-        <v>509</v>
+        <v>483</v>
       </c>
       <c r="K16" t="n">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="L16" t="n">
-        <v>497.7</v>
+        <v>470.7</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>470</v>
+        <v>426</v>
       </c>
       <c r="C17" t="n">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="D17" t="n">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="E17" t="n">
-        <v>434</v>
+        <v>461</v>
       </c>
       <c r="F17" t="n">
-        <v>491</v>
+        <v>551</v>
       </c>
       <c r="G17" t="n">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="H17" t="n">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="I17" t="n">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="J17" t="n">
-        <v>534</v>
+        <v>554</v>
       </c>
       <c r="K17" t="n">
-        <v>495</v>
+        <v>445</v>
       </c>
       <c r="L17" t="n">
-        <v>473.5</v>
+        <v>476.2</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>486</v>
+        <v>556</v>
       </c>
       <c r="C18" t="n">
-        <v>533</v>
+        <v>573</v>
       </c>
       <c r="D18" t="n">
-        <v>615</v>
+        <v>509</v>
       </c>
       <c r="E18" t="n">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="F18" t="n">
-        <v>564</v>
+        <v>540</v>
       </c>
       <c r="G18" t="n">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="H18" t="n">
-        <v>543</v>
+        <v>501</v>
       </c>
       <c r="I18" t="n">
-        <v>547</v>
+        <v>489</v>
       </c>
       <c r="J18" t="n">
         <v>575</v>
       </c>
       <c r="K18" t="n">
-        <v>593</v>
+        <v>562</v>
       </c>
       <c r="L18" t="n">
-        <v>557.5</v>
+        <v>542.4</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>536</v>
+        <v>493</v>
       </c>
       <c r="C19" t="n">
-        <v>573</v>
+        <v>504</v>
       </c>
       <c r="D19" t="n">
-        <v>503</v>
+        <v>488</v>
       </c>
       <c r="E19" t="n">
-        <v>491</v>
+        <v>466</v>
       </c>
       <c r="F19" t="n">
-        <v>576</v>
+        <v>476</v>
       </c>
       <c r="G19" t="n">
-        <v>530</v>
+        <v>495</v>
       </c>
       <c r="H19" t="n">
-        <v>502</v>
+        <v>462</v>
       </c>
       <c r="I19" t="n">
-        <v>554</v>
+        <v>492</v>
       </c>
       <c r="J19" t="n">
-        <v>522</v>
+        <v>485</v>
       </c>
       <c r="K19" t="n">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="L19" t="n">
-        <v>529.7</v>
+        <v>488.1</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>496</v>
+        <v>528</v>
       </c>
       <c r="C20" t="n">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="D20" t="n">
-        <v>523</v>
+        <v>537</v>
       </c>
       <c r="E20" t="n">
-        <v>455</v>
+        <v>532</v>
       </c>
       <c r="F20" t="n">
         <v>532</v>
       </c>
       <c r="G20" t="n">
-        <v>574</v>
+        <v>482</v>
       </c>
       <c r="H20" t="n">
-        <v>487</v>
+        <v>456</v>
       </c>
       <c r="I20" t="n">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="J20" t="n">
-        <v>438</v>
+        <v>522</v>
       </c>
       <c r="K20" t="n">
-        <v>486</v>
+        <v>458</v>
       </c>
       <c r="L20" t="n">
-        <v>493</v>
+        <v>502.7</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>467</v>
+        <v>528</v>
       </c>
       <c r="C21" t="n">
-        <v>420</v>
+        <v>509</v>
       </c>
       <c r="D21" t="n">
-        <v>521</v>
+        <v>468</v>
       </c>
       <c r="E21" t="n">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="F21" t="n">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="G21" t="n">
-        <v>464</v>
+        <v>580</v>
       </c>
       <c r="H21" t="n">
-        <v>499</v>
+        <v>475</v>
       </c>
       <c r="I21" t="n">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="J21" t="n">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="K21" t="n">
-        <v>465</v>
+        <v>502</v>
       </c>
       <c r="L21" t="n">
-        <v>478</v>
+        <v>500.6</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>542</v>
+        <v>473</v>
       </c>
       <c r="C22" t="n">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="D22" t="n">
-        <v>473</v>
+        <v>509</v>
       </c>
       <c r="E22" t="n">
-        <v>465</v>
+        <v>505</v>
       </c>
       <c r="F22" t="n">
-        <v>461</v>
+        <v>412</v>
       </c>
       <c r="G22" t="n">
-        <v>473</v>
+        <v>454</v>
       </c>
       <c r="H22" t="n">
-        <v>494</v>
+        <v>453</v>
       </c>
       <c r="I22" t="n">
-        <v>457</v>
+        <v>512</v>
       </c>
       <c r="J22" t="n">
-        <v>483</v>
+        <v>513</v>
       </c>
       <c r="K22" t="n">
-        <v>517</v>
+        <v>458</v>
       </c>
       <c r="L22" t="n">
-        <v>482.6</v>
+        <v>474.1</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>448</v>
+        <v>472</v>
       </c>
       <c r="C23" t="n">
-        <v>426</v>
+        <v>470</v>
       </c>
       <c r="D23" t="n">
-        <v>459</v>
+        <v>420</v>
       </c>
       <c r="E23" t="n">
-        <v>426</v>
+        <v>458</v>
       </c>
       <c r="F23" t="n">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="G23" t="n">
-        <v>439</v>
+        <v>387</v>
       </c>
       <c r="H23" t="n">
-        <v>438</v>
+        <v>467</v>
       </c>
       <c r="I23" t="n">
-        <v>448</v>
+        <v>484</v>
       </c>
       <c r="J23" t="n">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="K23" t="n">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L23" t="n">
-        <v>439.6</v>
+        <v>447.3</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="C24" t="n">
-        <v>421</v>
+        <v>532</v>
       </c>
       <c r="D24" t="n">
-        <v>462</v>
+        <v>434</v>
       </c>
       <c r="E24" t="n">
-        <v>442</v>
+        <v>477</v>
       </c>
       <c r="F24" t="n">
-        <v>445</v>
+        <v>527</v>
       </c>
       <c r="G24" t="n">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="H24" t="n">
-        <v>436</v>
+        <v>463</v>
       </c>
       <c r="I24" t="n">
-        <v>482</v>
+        <v>426</v>
       </c>
       <c r="J24" t="n">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K24" t="n">
-        <v>437</v>
+        <v>535</v>
       </c>
       <c r="L24" t="n">
-        <v>445.1</v>
+        <v>473.3</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="C25" t="n">
+        <v>429</v>
+      </c>
+      <c r="D25" t="n">
+        <v>397</v>
+      </c>
+      <c r="E25" t="n">
+        <v>422</v>
+      </c>
+      <c r="F25" t="n">
+        <v>383</v>
+      </c>
+      <c r="G25" t="n">
+        <v>397</v>
+      </c>
+      <c r="H25" t="n">
+        <v>439</v>
+      </c>
+      <c r="I25" t="n">
+        <v>409</v>
+      </c>
+      <c r="J25" t="n">
         <v>380</v>
       </c>
-      <c r="D25" t="n">
-        <v>405</v>
-      </c>
-      <c r="E25" t="n">
-        <v>432</v>
-      </c>
-      <c r="F25" t="n">
-        <v>457</v>
-      </c>
-      <c r="G25" t="n">
-        <v>437</v>
-      </c>
-      <c r="H25" t="n">
-        <v>413</v>
-      </c>
-      <c r="I25" t="n">
-        <v>375</v>
-      </c>
-      <c r="J25" t="n">
-        <v>393</v>
-      </c>
       <c r="K25" t="n">
-        <v>409</v>
+        <v>485</v>
       </c>
       <c r="L25" t="n">
-        <v>410.4</v>
+        <v>416.2</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>542</v>
+        <v>555</v>
       </c>
       <c r="C26" t="n">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="D26" t="n">
-        <v>479</v>
+        <v>630</v>
       </c>
       <c r="E26" t="n">
-        <v>565</v>
+        <v>643</v>
       </c>
       <c r="F26" t="n">
-        <v>590</v>
+        <v>534</v>
       </c>
       <c r="G26" t="n">
-        <v>623</v>
+        <v>569</v>
       </c>
       <c r="H26" t="n">
-        <v>616</v>
+        <v>653</v>
       </c>
       <c r="I26" t="n">
-        <v>556</v>
+        <v>607</v>
       </c>
       <c r="J26" t="n">
-        <v>594</v>
+        <v>548</v>
       </c>
       <c r="K26" t="n">
-        <v>489</v>
+        <v>667</v>
       </c>
       <c r="L26" t="n">
-        <v>567.5</v>
+        <v>603.6</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="C27" t="n">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="D27" t="n">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="E27" t="n">
-        <v>457</v>
+        <v>410</v>
       </c>
       <c r="F27" t="n">
-        <v>414</v>
+        <v>445</v>
       </c>
       <c r="G27" t="n">
+        <v>405</v>
+      </c>
+      <c r="H27" t="n">
         <v>415</v>
       </c>
-      <c r="H27" t="n">
-        <v>405</v>
-      </c>
       <c r="I27" t="n">
-        <v>401</v>
+        <v>446</v>
       </c>
       <c r="J27" t="n">
-        <v>399</v>
+        <v>456</v>
       </c>
       <c r="K27" t="n">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="L27" t="n">
-        <v>416</v>
+        <v>421.6</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="C28" t="n">
-        <v>480</v>
+        <v>439</v>
       </c>
       <c r="D28" t="n">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E28" t="n">
-        <v>418</v>
+        <v>482</v>
       </c>
       <c r="F28" t="n">
+        <v>476</v>
+      </c>
+      <c r="G28" t="n">
+        <v>436</v>
+      </c>
+      <c r="H28" t="n">
+        <v>454</v>
+      </c>
+      <c r="I28" t="n">
+        <v>499</v>
+      </c>
+      <c r="J28" t="n">
+        <v>433</v>
+      </c>
+      <c r="K28" t="n">
         <v>463</v>
       </c>
-      <c r="G28" t="n">
-        <v>440</v>
-      </c>
-      <c r="H28" t="n">
-        <v>432</v>
-      </c>
-      <c r="I28" t="n">
-        <v>431</v>
-      </c>
-      <c r="J28" t="n">
-        <v>492</v>
-      </c>
-      <c r="K28" t="n">
-        <v>478</v>
-      </c>
       <c r="L28" t="n">
-        <v>454.5</v>
+        <v>458.2</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="C29" t="n">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="D29" t="n">
-        <v>420</v>
+        <v>452</v>
       </c>
       <c r="E29" t="n">
-        <v>433</v>
+        <v>504</v>
       </c>
       <c r="F29" t="n">
-        <v>445</v>
+        <v>482</v>
       </c>
       <c r="G29" t="n">
+        <v>465</v>
+      </c>
+      <c r="H29" t="n">
         <v>473</v>
       </c>
-      <c r="H29" t="n">
-        <v>445</v>
-      </c>
       <c r="I29" t="n">
-        <v>481</v>
+        <v>458</v>
       </c>
       <c r="J29" t="n">
-        <v>469</v>
+        <v>432</v>
       </c>
       <c r="K29" t="n">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="L29" t="n">
-        <v>453.1</v>
+        <v>464.7</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
+        <v>435</v>
+      </c>
+      <c r="C30" t="n">
+        <v>413</v>
+      </c>
+      <c r="D30" t="n">
         <v>462</v>
       </c>
-      <c r="C30" t="n">
-        <v>369</v>
-      </c>
-      <c r="D30" t="n">
-        <v>483</v>
-      </c>
       <c r="E30" t="n">
-        <v>499</v>
+        <v>588</v>
       </c>
       <c r="F30" t="n">
-        <v>426</v>
+        <v>489</v>
       </c>
       <c r="G30" t="n">
-        <v>508</v>
+        <v>392</v>
       </c>
       <c r="H30" t="n">
-        <v>440</v>
+        <v>489</v>
       </c>
       <c r="I30" t="n">
-        <v>483</v>
+        <v>451</v>
       </c>
       <c r="J30" t="n">
-        <v>492</v>
+        <v>446</v>
       </c>
       <c r="K30" t="n">
-        <v>457</v>
+        <v>421</v>
       </c>
       <c r="L30" t="n">
-        <v>461.9</v>
+        <v>458.6</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>483</v>
+        <v>452</v>
       </c>
       <c r="C31" t="n">
-        <v>461</v>
+        <v>420</v>
       </c>
       <c r="D31" t="n">
-        <v>498</v>
+        <v>470</v>
       </c>
       <c r="E31" t="n">
-        <v>486</v>
+        <v>454</v>
       </c>
       <c r="F31" t="n">
-        <v>458</v>
+        <v>437</v>
       </c>
       <c r="G31" t="n">
+        <v>454</v>
+      </c>
+      <c r="H31" t="n">
+        <v>472</v>
+      </c>
+      <c r="I31" t="n">
+        <v>445</v>
+      </c>
+      <c r="J31" t="n">
+        <v>422</v>
+      </c>
+      <c r="K31" t="n">
         <v>432</v>
       </c>
-      <c r="H31" t="n">
-        <v>473</v>
-      </c>
-      <c r="I31" t="n">
-        <v>426</v>
-      </c>
-      <c r="J31" t="n">
-        <v>464</v>
-      </c>
-      <c r="K31" t="n">
-        <v>506</v>
-      </c>
       <c r="L31" t="n">
-        <v>468.7</v>
+        <v>445.8</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="C32" t="n">
+        <v>490</v>
+      </c>
+      <c r="D32" t="n">
+        <v>421</v>
+      </c>
+      <c r="E32" t="n">
+        <v>405</v>
+      </c>
+      <c r="F32" t="n">
+        <v>377</v>
+      </c>
+      <c r="G32" t="n">
         <v>446</v>
       </c>
-      <c r="D32" t="n">
-        <v>409</v>
-      </c>
-      <c r="E32" t="n">
-        <v>409</v>
-      </c>
-      <c r="F32" t="n">
-        <v>420</v>
-      </c>
-      <c r="G32" t="n">
-        <v>432</v>
-      </c>
       <c r="H32" t="n">
-        <v>402</v>
+        <v>461</v>
       </c>
       <c r="I32" t="n">
-        <v>395</v>
+        <v>490</v>
       </c>
       <c r="J32" t="n">
-        <v>437</v>
+        <v>555</v>
       </c>
       <c r="K32" t="n">
-        <v>437</v>
+        <v>403</v>
       </c>
       <c r="L32" t="n">
-        <v>418.8</v>
+        <v>446.1</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>542</v>
+        <v>464</v>
       </c>
       <c r="C33" t="n">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="D33" t="n">
-        <v>490</v>
+        <v>380</v>
       </c>
       <c r="E33" t="n">
-        <v>457</v>
+        <v>393</v>
       </c>
       <c r="F33" t="n">
-        <v>405</v>
+        <v>506</v>
       </c>
       <c r="G33" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="H33" t="n">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="I33" t="n">
-        <v>429</v>
+        <v>390</v>
       </c>
       <c r="J33" t="n">
-        <v>368</v>
+        <v>461</v>
       </c>
       <c r="K33" t="n">
-        <v>414</v>
+        <v>479</v>
       </c>
       <c r="L33" t="n">
-        <v>444.1</v>
+        <v>442.3</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>475</v>
+        <v>426</v>
       </c>
       <c r="C34" t="n">
-        <v>399</v>
+        <v>455</v>
       </c>
       <c r="D34" t="n">
-        <v>491</v>
+        <v>472</v>
       </c>
       <c r="E34" t="n">
-        <v>389</v>
+        <v>504</v>
       </c>
       <c r="F34" t="n">
-        <v>433</v>
+        <v>403</v>
       </c>
       <c r="G34" t="n">
-        <v>430</v>
+        <v>411</v>
       </c>
       <c r="H34" t="n">
-        <v>417</v>
+        <v>451</v>
       </c>
       <c r="I34" t="n">
-        <v>388</v>
+        <v>431</v>
       </c>
       <c r="J34" t="n">
-        <v>449</v>
+        <v>416</v>
       </c>
       <c r="K34" t="n">
-        <v>419</v>
+        <v>453</v>
       </c>
       <c r="L34" t="n">
-        <v>429</v>
+        <v>442.2</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>439</v>
+        <v>481</v>
       </c>
       <c r="C35" t="n">
+        <v>510</v>
+      </c>
+      <c r="D35" t="n">
+        <v>471</v>
+      </c>
+      <c r="E35" t="n">
+        <v>492</v>
+      </c>
+      <c r="F35" t="n">
+        <v>508</v>
+      </c>
+      <c r="G35" t="n">
+        <v>492</v>
+      </c>
+      <c r="H35" t="n">
+        <v>451</v>
+      </c>
+      <c r="I35" t="n">
         <v>431</v>
       </c>
-      <c r="D35" t="n">
-        <v>438</v>
-      </c>
-      <c r="E35" t="n">
-        <v>450</v>
-      </c>
-      <c r="F35" t="n">
-        <v>527</v>
-      </c>
-      <c r="G35" t="n">
-        <v>471</v>
-      </c>
-      <c r="H35" t="n">
-        <v>504</v>
-      </c>
-      <c r="I35" t="n">
-        <v>494</v>
-      </c>
       <c r="J35" t="n">
-        <v>421</v>
+        <v>584</v>
       </c>
       <c r="K35" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L35" t="n">
-        <v>467.8</v>
+        <v>492.5</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C36" t="n">
-        <v>343</v>
+        <v>372</v>
       </c>
       <c r="D36" t="n">
-        <v>403</v>
+        <v>450</v>
       </c>
       <c r="E36" t="n">
-        <v>396</v>
+        <v>437</v>
       </c>
       <c r="F36" t="n">
-        <v>392</v>
+        <v>367</v>
       </c>
       <c r="G36" t="n">
-        <v>425</v>
+        <v>469</v>
       </c>
       <c r="H36" t="n">
-        <v>408</v>
+        <v>376</v>
       </c>
       <c r="I36" t="n">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="J36" t="n">
-        <v>436</v>
+        <v>483</v>
       </c>
       <c r="K36" t="n">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="L36" t="n">
-        <v>402.2</v>
+        <v>414</v>
       </c>
     </row>
     <row r="37">
@@ -1801,34 +1801,34 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>408</v>
+        <v>473</v>
       </c>
       <c r="C37" t="n">
-        <v>399</v>
+        <v>460</v>
       </c>
       <c r="D37" t="n">
-        <v>597</v>
+        <v>454</v>
       </c>
       <c r="E37" t="n">
-        <v>422</v>
+        <v>455</v>
       </c>
       <c r="F37" t="n">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="G37" t="n">
-        <v>520</v>
+        <v>458</v>
       </c>
       <c r="H37" t="n">
-        <v>476</v>
+        <v>518</v>
       </c>
       <c r="I37" t="n">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="J37" t="n">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="K37" t="n">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="L37" t="n">
         <v>472</v>
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
+        <v>530</v>
+      </c>
+      <c r="C38" t="n">
+        <v>560</v>
+      </c>
+      <c r="D38" t="n">
         <v>554</v>
       </c>
-      <c r="C38" t="n">
-        <v>500</v>
-      </c>
-      <c r="D38" t="n">
-        <v>501</v>
-      </c>
       <c r="E38" t="n">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="F38" t="n">
-        <v>466</v>
+        <v>541</v>
       </c>
       <c r="G38" t="n">
-        <v>472</v>
+        <v>625</v>
       </c>
       <c r="H38" t="n">
-        <v>552</v>
+        <v>572</v>
       </c>
       <c r="I38" t="n">
-        <v>623</v>
+        <v>571</v>
       </c>
       <c r="J38" t="n">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="K38" t="n">
-        <v>567</v>
+        <v>601</v>
       </c>
       <c r="L38" t="n">
-        <v>533.1</v>
+        <v>563.9</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>389</v>
+        <v>426</v>
       </c>
       <c r="C39" t="n">
-        <v>471</v>
+        <v>450</v>
       </c>
       <c r="D39" t="n">
-        <v>417</v>
+        <v>482</v>
       </c>
       <c r="E39" t="n">
-        <v>370</v>
+        <v>426</v>
       </c>
       <c r="F39" t="n">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="G39" t="n">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="H39" t="n">
-        <v>494</v>
+        <v>460</v>
       </c>
       <c r="I39" t="n">
-        <v>420</v>
+        <v>385</v>
       </c>
       <c r="J39" t="n">
-        <v>396</v>
+        <v>446</v>
       </c>
       <c r="K39" t="n">
-        <v>418</v>
+        <v>449</v>
       </c>
       <c r="L39" t="n">
-        <v>422.9</v>
+        <v>438.8</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
+        <v>496</v>
+      </c>
+      <c r="C40" t="n">
+        <v>474</v>
+      </c>
+      <c r="D40" t="n">
+        <v>500</v>
+      </c>
+      <c r="E40" t="n">
+        <v>464</v>
+      </c>
+      <c r="F40" t="n">
         <v>460</v>
       </c>
-      <c r="C40" t="n">
-        <v>511</v>
-      </c>
-      <c r="D40" t="n">
-        <v>469</v>
-      </c>
-      <c r="E40" t="n">
-        <v>481</v>
-      </c>
-      <c r="F40" t="n">
-        <v>479</v>
-      </c>
       <c r="G40" t="n">
-        <v>515</v>
+        <v>484</v>
       </c>
       <c r="H40" t="n">
-        <v>452</v>
+        <v>428</v>
       </c>
       <c r="I40" t="n">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="J40" t="n">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="K40" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="L40" t="n">
-        <v>472.9</v>
+        <v>467.4</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>522</v>
+        <v>430</v>
       </c>
       <c r="C41" t="n">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="D41" t="n">
-        <v>516</v>
+        <v>491</v>
       </c>
       <c r="E41" t="n">
-        <v>503</v>
+        <v>458</v>
       </c>
       <c r="F41" t="n">
-        <v>562</v>
+        <v>483</v>
       </c>
       <c r="G41" t="n">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="H41" t="n">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="I41" t="n">
-        <v>484</v>
+        <v>514</v>
       </c>
       <c r="J41" t="n">
-        <v>573</v>
+        <v>497</v>
       </c>
       <c r="K41" t="n">
-        <v>509</v>
+        <v>552</v>
       </c>
       <c r="L41" t="n">
-        <v>525.3</v>
+        <v>498.9</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>418</v>
+        <v>477</v>
       </c>
       <c r="C42" t="n">
-        <v>521</v>
+        <v>503</v>
       </c>
       <c r="D42" t="n">
-        <v>428</v>
+        <v>462</v>
       </c>
       <c r="E42" t="n">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="F42" t="n">
-        <v>467</v>
+        <v>486</v>
       </c>
       <c r="G42" t="n">
-        <v>469</v>
+        <v>497</v>
       </c>
       <c r="H42" t="n">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="I42" t="n">
-        <v>493</v>
+        <v>457</v>
       </c>
       <c r="J42" t="n">
-        <v>528</v>
+        <v>434</v>
       </c>
       <c r="K42" t="n">
-        <v>547</v>
+        <v>514</v>
       </c>
       <c r="L42" t="n">
-        <v>480.3</v>
+        <v>476.3</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
+        <v>499</v>
+      </c>
+      <c r="C43" t="n">
+        <v>561</v>
+      </c>
+      <c r="D43" t="n">
+        <v>440</v>
+      </c>
+      <c r="E43" t="n">
         <v>502</v>
       </c>
-      <c r="C43" t="n">
-        <v>456</v>
-      </c>
-      <c r="D43" t="n">
-        <v>450</v>
-      </c>
-      <c r="E43" t="n">
-        <v>486</v>
-      </c>
       <c r="F43" t="n">
-        <v>534</v>
+        <v>464</v>
       </c>
       <c r="G43" t="n">
-        <v>488</v>
+        <v>462</v>
       </c>
       <c r="H43" t="n">
-        <v>489</v>
+        <v>527</v>
       </c>
       <c r="I43" t="n">
-        <v>456</v>
+        <v>491</v>
       </c>
       <c r="J43" t="n">
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="K43" t="n">
-        <v>500</v>
+        <v>408</v>
       </c>
       <c r="L43" t="n">
-        <v>485.1</v>
+        <v>485.8</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="C44" t="n">
-        <v>467</v>
+        <v>487</v>
       </c>
       <c r="D44" t="n">
-        <v>465</v>
+        <v>428</v>
       </c>
       <c r="E44" t="n">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="F44" t="n">
-        <v>454</v>
+        <v>478</v>
       </c>
       <c r="G44" t="n">
+        <v>515</v>
+      </c>
+      <c r="H44" t="n">
         <v>435</v>
       </c>
-      <c r="H44" t="n">
-        <v>450</v>
-      </c>
       <c r="I44" t="n">
-        <v>443</v>
+        <v>474</v>
       </c>
       <c r="J44" t="n">
-        <v>438</v>
+        <v>498</v>
       </c>
       <c r="K44" t="n">
-        <v>519</v>
+        <v>419</v>
       </c>
       <c r="L44" t="n">
-        <v>454.3</v>
+        <v>463.4</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
+        <v>513</v>
+      </c>
+      <c r="C45" t="n">
+        <v>465</v>
+      </c>
+      <c r="D45" t="n">
+        <v>547</v>
+      </c>
+      <c r="E45" t="n">
+        <v>513</v>
+      </c>
+      <c r="F45" t="n">
+        <v>446</v>
+      </c>
+      <c r="G45" t="n">
+        <v>430</v>
+      </c>
+      <c r="H45" t="n">
+        <v>448</v>
+      </c>
+      <c r="I45" t="n">
         <v>524</v>
       </c>
-      <c r="C45" t="n">
-        <v>517</v>
-      </c>
-      <c r="D45" t="n">
-        <v>541</v>
-      </c>
-      <c r="E45" t="n">
-        <v>541</v>
-      </c>
-      <c r="F45" t="n">
-        <v>488</v>
-      </c>
-      <c r="G45" t="n">
-        <v>509</v>
-      </c>
-      <c r="H45" t="n">
-        <v>452</v>
-      </c>
-      <c r="I45" t="n">
-        <v>490</v>
-      </c>
       <c r="J45" t="n">
-        <v>431</v>
+        <v>474</v>
       </c>
       <c r="K45" t="n">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="L45" t="n">
-        <v>497.5</v>
+        <v>484.7</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="C46" t="n">
-        <v>458</v>
+        <v>442</v>
       </c>
       <c r="D46" t="n">
-        <v>448</v>
+        <v>341</v>
       </c>
       <c r="E46" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F46" t="n">
-        <v>372</v>
+        <v>476</v>
       </c>
       <c r="G46" t="n">
-        <v>369</v>
+        <v>430</v>
       </c>
       <c r="H46" t="n">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="I46" t="n">
-        <v>445</v>
+        <v>381</v>
       </c>
       <c r="J46" t="n">
-        <v>489</v>
+        <v>428</v>
       </c>
       <c r="K46" t="n">
-        <v>401</v>
+        <v>431</v>
       </c>
       <c r="L46" t="n">
-        <v>419</v>
+        <v>413.9</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>534</v>
+        <v>577</v>
       </c>
       <c r="C47" t="n">
-        <v>541</v>
+        <v>526</v>
       </c>
       <c r="D47" t="n">
-        <v>541</v>
+        <v>484</v>
       </c>
       <c r="E47" t="n">
-        <v>654</v>
+        <v>536</v>
       </c>
       <c r="F47" t="n">
-        <v>537</v>
+        <v>497</v>
       </c>
       <c r="G47" t="n">
-        <v>515</v>
+        <v>578</v>
       </c>
       <c r="H47" t="n">
-        <v>469</v>
+        <v>624</v>
       </c>
       <c r="I47" t="n">
-        <v>504</v>
+        <v>458</v>
       </c>
       <c r="J47" t="n">
-        <v>600</v>
+        <v>531</v>
       </c>
       <c r="K47" t="n">
-        <v>537</v>
+        <v>485</v>
       </c>
       <c r="L47" t="n">
-        <v>543.2</v>
+        <v>529.6</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>547</v>
+        <v>506</v>
       </c>
       <c r="C48" t="n">
-        <v>545</v>
+        <v>505</v>
       </c>
       <c r="D48" t="n">
-        <v>543</v>
+        <v>518</v>
       </c>
       <c r="E48" t="n">
-        <v>582</v>
+        <v>506</v>
       </c>
       <c r="F48" t="n">
-        <v>475</v>
+        <v>517</v>
       </c>
       <c r="G48" t="n">
         <v>520</v>
       </c>
       <c r="H48" t="n">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="I48" t="n">
-        <v>505</v>
+        <v>554</v>
       </c>
       <c r="J48" t="n">
-        <v>508</v>
+        <v>490</v>
       </c>
       <c r="K48" t="n">
-        <v>488</v>
+        <v>521</v>
       </c>
       <c r="L48" t="n">
-        <v>525</v>
+        <v>517.3</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>554</v>
+        <v>471</v>
       </c>
       <c r="C49" t="n">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="D49" t="n">
-        <v>521</v>
+        <v>449</v>
       </c>
       <c r="E49" t="n">
-        <v>484</v>
+        <v>442</v>
       </c>
       <c r="F49" t="n">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="G49" t="n">
-        <v>440</v>
+        <v>467</v>
       </c>
       <c r="H49" t="n">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="I49" t="n">
-        <v>507</v>
+        <v>538</v>
       </c>
       <c r="J49" t="n">
-        <v>595</v>
+        <v>467</v>
       </c>
       <c r="K49" t="n">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="L49" t="n">
-        <v>494.5</v>
+        <v>471.8</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C50" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="D50" t="n">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="E50" t="n">
-        <v>385</v>
+        <v>418</v>
       </c>
       <c r="F50" t="n">
-        <v>414</v>
+        <v>443</v>
       </c>
       <c r="G50" t="n">
-        <v>466</v>
+        <v>487</v>
       </c>
       <c r="H50" t="n">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="I50" t="n">
-        <v>387</v>
+        <v>434</v>
       </c>
       <c r="J50" t="n">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="K50" t="n">
-        <v>441</v>
+        <v>483</v>
       </c>
       <c r="L50" t="n">
-        <v>435.3</v>
+        <v>453.3</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
+        <v>412</v>
+      </c>
+      <c r="C51" t="n">
+        <v>480</v>
+      </c>
+      <c r="D51" t="n">
+        <v>505</v>
+      </c>
+      <c r="E51" t="n">
+        <v>406</v>
+      </c>
+      <c r="F51" t="n">
+        <v>433</v>
+      </c>
+      <c r="G51" t="n">
+        <v>430</v>
+      </c>
+      <c r="H51" t="n">
         <v>421</v>
       </c>
-      <c r="C51" t="n">
-        <v>414</v>
-      </c>
-      <c r="D51" t="n">
-        <v>456</v>
-      </c>
-      <c r="E51" t="n">
-        <v>444</v>
-      </c>
-      <c r="F51" t="n">
-        <v>466</v>
-      </c>
-      <c r="G51" t="n">
-        <v>460</v>
-      </c>
-      <c r="H51" t="n">
-        <v>465</v>
-      </c>
       <c r="I51" t="n">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="J51" t="n">
-        <v>451</v>
+        <v>424</v>
       </c>
       <c r="K51" t="n">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="L51" t="n">
-        <v>441.1</v>
+        <v>434.3</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>473.96</v>
+        <v>468.02</v>
       </c>
       <c r="C52" t="n">
-        <v>475.38</v>
+        <v>481.1</v>
       </c>
       <c r="D52" t="n">
-        <v>488.04</v>
+        <v>473.22</v>
       </c>
       <c r="E52" t="n">
-        <v>477.38</v>
+        <v>478.14</v>
       </c>
       <c r="F52" t="n">
-        <v>477.68</v>
+        <v>475.56</v>
       </c>
       <c r="G52" t="n">
-        <v>481.56</v>
+        <v>478.3</v>
       </c>
       <c r="H52" t="n">
-        <v>478.32</v>
+        <v>482.76</v>
       </c>
       <c r="I52" t="n">
-        <v>474.24</v>
+        <v>474.8</v>
       </c>
       <c r="J52" t="n">
-        <v>481.42</v>
+        <v>489.04</v>
       </c>
       <c r="K52" t="n">
-        <v>475.22</v>
+        <v>481</v>
       </c>
       <c r="L52" t="n">
-        <v>478.3199999999999</v>
+        <v>478.194</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2.466902732849121</v>
+        <v>2.278738737106323</v>
       </c>
       <c r="C2" t="n">
-        <v>2.025818347930908</v>
+        <v>2.187275409698486</v>
       </c>
       <c r="D2" t="n">
-        <v>2.133061647415161</v>
+        <v>2.230219602584839</v>
       </c>
       <c r="E2" t="n">
-        <v>1.991923570632935</v>
+        <v>2.248543262481689</v>
       </c>
       <c r="F2" t="n">
-        <v>1.968985795974731</v>
+        <v>2.120063304901123</v>
       </c>
       <c r="G2" t="n">
-        <v>2.176936149597168</v>
+        <v>2.214887142181396</v>
       </c>
       <c r="H2" t="n">
-        <v>2.095562696456909</v>
+        <v>2.225245714187622</v>
       </c>
       <c r="I2" t="n">
-        <v>2.160377025604248</v>
+        <v>2.16635537147522</v>
       </c>
       <c r="J2" t="n">
-        <v>2.034700870513916</v>
+        <v>2.23865270614624</v>
       </c>
       <c r="K2" t="n">
-        <v>2.060153484344482</v>
+        <v>2.274823665618896</v>
       </c>
       <c r="L2" t="n">
-        <v>2.111442232131958</v>
+        <v>2.218480491638184</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>2.220211505889893</v>
+        <v>2.368668556213379</v>
       </c>
       <c r="C3" t="n">
-        <v>2.21024751663208</v>
+        <v>2.581728458404541</v>
       </c>
       <c r="D3" t="n">
-        <v>2.350373506546021</v>
+        <v>2.329627752304077</v>
       </c>
       <c r="E3" t="n">
-        <v>2.24565052986145</v>
+        <v>2.364096164703369</v>
       </c>
       <c r="F3" t="n">
-        <v>2.577784299850464</v>
+        <v>2.458409309387207</v>
       </c>
       <c r="G3" t="n">
-        <v>2.134460687637329</v>
+        <v>2.607646942138672</v>
       </c>
       <c r="H3" t="n">
-        <v>2.478531122207642</v>
+        <v>2.571992635726929</v>
       </c>
       <c r="I3" t="n">
-        <v>2.53639817237854</v>
+        <v>2.490291357040405</v>
       </c>
       <c r="J3" t="n">
-        <v>2.521945714950562</v>
+        <v>2.497060775756836</v>
       </c>
       <c r="K3" t="n">
-        <v>2.517932415008545</v>
+        <v>3.666292667388916</v>
       </c>
       <c r="L3" t="n">
-        <v>2.379353547096252</v>
+        <v>2.593581461906433</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>2.463099956512451</v>
+        <v>2.575742244720459</v>
       </c>
       <c r="C4" t="n">
-        <v>2.512959480285645</v>
+        <v>2.587438344955444</v>
       </c>
       <c r="D4" t="n">
-        <v>2.388265371322632</v>
+        <v>2.506190776824951</v>
       </c>
       <c r="E4" t="n">
-        <v>2.536413192749023</v>
+        <v>2.575574398040771</v>
       </c>
       <c r="F4" t="n">
-        <v>2.593249559402466</v>
+        <v>2.592665910720825</v>
       </c>
       <c r="G4" t="n">
-        <v>2.450631141662598</v>
+        <v>2.503942966461182</v>
       </c>
       <c r="H4" t="n">
-        <v>2.385776996612549</v>
+        <v>2.516766548156738</v>
       </c>
       <c r="I4" t="n">
-        <v>2.401738882064819</v>
+        <v>2.449759721755981</v>
       </c>
       <c r="J4" t="n">
-        <v>2.357349157333374</v>
+        <v>2.366376876831055</v>
       </c>
       <c r="K4" t="n">
-        <v>2.220711231231689</v>
+        <v>2.578334331512451</v>
       </c>
       <c r="L4" t="n">
-        <v>2.431019496917725</v>
+        <v>2.525279211997986</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>2.07459020614624</v>
+        <v>2.171664953231812</v>
       </c>
       <c r="C5" t="n">
-        <v>2.139433145523071</v>
+        <v>2.262609958648682</v>
       </c>
       <c r="D5" t="n">
-        <v>2.038684606552124</v>
+        <v>2.229957103729248</v>
       </c>
       <c r="E5" t="n">
-        <v>2.079083204269409</v>
+        <v>2.260246515274048</v>
       </c>
       <c r="F5" t="n">
-        <v>2.15788459777832</v>
+        <v>2.309175729751587</v>
       </c>
       <c r="G5" t="n">
-        <v>2.111000061035156</v>
+        <v>2.263839483261108</v>
       </c>
       <c r="H5" t="n">
-        <v>2.12297248840332</v>
+        <v>2.378978252410889</v>
       </c>
       <c r="I5" t="n">
-        <v>2.122476816177368</v>
+        <v>2.260872364044189</v>
       </c>
       <c r="J5" t="n">
-        <v>2.194297313690186</v>
+        <v>2.520246982574463</v>
       </c>
       <c r="K5" t="n">
-        <v>2.171868085861206</v>
+        <v>2.363775730133057</v>
       </c>
       <c r="L5" t="n">
-        <v>2.12122905254364</v>
+        <v>2.302136707305908</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>2.001788139343262</v>
+        <v>2.093852758407593</v>
       </c>
       <c r="C6" t="n">
-        <v>2.196271181106567</v>
+        <v>2.26227879524231</v>
       </c>
       <c r="D6" t="n">
-        <v>1.860651731491089</v>
+        <v>2.273221731185913</v>
       </c>
       <c r="E6" t="n">
-        <v>1.926476716995239</v>
+        <v>2.047611951828003</v>
       </c>
       <c r="F6" t="n">
-        <v>2.032704591751099</v>
+        <v>1.984211921691895</v>
       </c>
       <c r="G6" t="n">
-        <v>2.120973348617554</v>
+        <v>2.071523427963257</v>
       </c>
       <c r="H6" t="n">
-        <v>1.899551153182983</v>
+        <v>2.117382526397705</v>
       </c>
       <c r="I6" t="n">
-        <v>1.850677967071533</v>
+        <v>2.235421180725098</v>
       </c>
       <c r="J6" t="n">
-        <v>1.881608724594116</v>
+        <v>2.379036903381348</v>
       </c>
       <c r="K6" t="n">
-        <v>1.930471658706665</v>
+        <v>2.427308559417725</v>
       </c>
       <c r="L6" t="n">
-        <v>1.970117521286011</v>
+        <v>2.189184975624085</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>2.306561470031738</v>
+        <v>2.49406361579895</v>
       </c>
       <c r="C7" t="n">
-        <v>2.428677558898926</v>
+        <v>2.453632354736328</v>
       </c>
       <c r="D7" t="n">
-        <v>2.538905382156372</v>
+        <v>2.447248935699463</v>
       </c>
       <c r="E7" t="n">
-        <v>2.457108497619629</v>
+        <v>2.57910680770874</v>
       </c>
       <c r="F7" t="n">
-        <v>2.278106451034546</v>
+        <v>2.587289571762085</v>
       </c>
       <c r="G7" t="n">
-        <v>2.592264413833618</v>
+        <v>2.437770128250122</v>
       </c>
       <c r="H7" t="n">
-        <v>2.634164571762085</v>
+        <v>2.451877593994141</v>
       </c>
       <c r="I7" t="n">
-        <v>2.59756326675415</v>
+        <v>2.38517427444458</v>
       </c>
       <c r="J7" t="n">
-        <v>2.248266220092773</v>
+        <v>2.481194734573364</v>
       </c>
       <c r="K7" t="n">
-        <v>2.243781328201294</v>
+        <v>2.472950458526611</v>
       </c>
       <c r="L7" t="n">
-        <v>2.432539916038513</v>
+        <v>2.479030847549438</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>2.345511198043823</v>
+        <v>2.461507558822632</v>
       </c>
       <c r="C8" t="n">
-        <v>2.906986951828003</v>
+        <v>2.598512649536133</v>
       </c>
       <c r="D8" t="n">
-        <v>2.48250412940979</v>
+        <v>2.417573928833008</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4029221534729</v>
+        <v>2.343255281448364</v>
       </c>
       <c r="F8" t="n">
-        <v>2.419836282730103</v>
+        <v>2.468557834625244</v>
       </c>
       <c r="G8" t="n">
-        <v>3.189964532852173</v>
+        <v>2.659713268280029</v>
       </c>
       <c r="H8" t="n">
-        <v>2.982470035552979</v>
+        <v>2.526070117950439</v>
       </c>
       <c r="I8" t="n">
-        <v>3.078258275985718</v>
+        <v>2.485572099685669</v>
       </c>
       <c r="J8" t="n">
-        <v>3.238649845123291</v>
+        <v>2.371024608612061</v>
       </c>
       <c r="K8" t="n">
-        <v>2.417755365371704</v>
+        <v>2.534295320510864</v>
       </c>
       <c r="L8" t="n">
-        <v>2.746485877037048</v>
+        <v>2.486608266830444</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32246470451355</v>
+        <v>2.356831073760986</v>
       </c>
       <c r="C9" t="n">
-        <v>2.315475463867188</v>
+        <v>2.303187608718872</v>
       </c>
       <c r="D9" t="n">
-        <v>2.226710557937622</v>
+        <v>2.241607427597046</v>
       </c>
       <c r="E9" t="n">
-        <v>2.298565864562988</v>
+        <v>2.527965784072876</v>
       </c>
       <c r="F9" t="n">
-        <v>2.190796375274658</v>
+        <v>2.404057025909424</v>
       </c>
       <c r="G9" t="n">
-        <v>2.864193201065063</v>
+        <v>2.344137668609619</v>
       </c>
       <c r="H9" t="n">
-        <v>2.760077476501465</v>
+        <v>2.330593585968018</v>
       </c>
       <c r="I9" t="n">
-        <v>2.757022857666016</v>
+        <v>2.360639333724976</v>
       </c>
       <c r="J9" t="n">
-        <v>2.396797657012939</v>
+        <v>2.406208038330078</v>
       </c>
       <c r="K9" t="n">
-        <v>2.172347545623779</v>
+        <v>2.201029300689697</v>
       </c>
       <c r="L9" t="n">
-        <v>2.430445170402527</v>
+        <v>2.347625684738159</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>2.393514156341553</v>
+        <v>2.262501239776611</v>
       </c>
       <c r="C10" t="n">
-        <v>2.51198410987854</v>
+        <v>2.302809476852417</v>
       </c>
       <c r="D10" t="n">
-        <v>2.275100946426392</v>
+        <v>2.461999893188477</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7720046043396</v>
+        <v>2.417055368423462</v>
       </c>
       <c r="F10" t="n">
-        <v>2.540063858032227</v>
+        <v>2.304548978805542</v>
       </c>
       <c r="G10" t="n">
-        <v>2.44134521484375</v>
+        <v>2.342410087585449</v>
       </c>
       <c r="H10" t="n">
-        <v>2.641382217407227</v>
+        <v>2.531504392623901</v>
       </c>
       <c r="I10" t="n">
-        <v>2.976470470428467</v>
+        <v>2.562860012054443</v>
       </c>
       <c r="J10" t="n">
-        <v>2.385488986968994</v>
+        <v>2.505133390426636</v>
       </c>
       <c r="K10" t="n">
-        <v>2.466104507446289</v>
+        <v>2.391142606735229</v>
       </c>
       <c r="L10" t="n">
-        <v>2.540345907211304</v>
+        <v>2.408196544647217</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>1.937825679779053</v>
+        <v>1.998308897018433</v>
       </c>
       <c r="C11" t="n">
-        <v>2.172996997833252</v>
+        <v>2.04910135269165</v>
       </c>
       <c r="D11" t="n">
-        <v>2.229886531829834</v>
+        <v>2.036373853683472</v>
       </c>
       <c r="E11" t="n">
-        <v>2.177956581115723</v>
+        <v>2.02453088760376</v>
       </c>
       <c r="F11" t="n">
-        <v>2.336126327514648</v>
+        <v>2.063542127609253</v>
       </c>
       <c r="G11" t="n">
-        <v>2.420917272567749</v>
+        <v>2.066816568374634</v>
       </c>
       <c r="H11" t="n">
-        <v>2.195428609848022</v>
+        <v>2.005579233169556</v>
       </c>
       <c r="I11" t="n">
-        <v>2.277220487594604</v>
+        <v>2.011679887771606</v>
       </c>
       <c r="J11" t="n">
-        <v>1.820866107940674</v>
+        <v>2.071047067642212</v>
       </c>
       <c r="K11" t="n">
-        <v>2.004904747009277</v>
+        <v>2.346719264984131</v>
       </c>
       <c r="L11" t="n">
-        <v>2.157412934303284</v>
+        <v>2.067369914054871</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>2.379464387893677</v>
+        <v>2.368802309036255</v>
       </c>
       <c r="C12" t="n">
-        <v>2.550359725952148</v>
+        <v>2.712875604629517</v>
       </c>
       <c r="D12" t="n">
-        <v>2.474726438522339</v>
+        <v>2.528956174850464</v>
       </c>
       <c r="E12" t="n">
-        <v>2.300645351409912</v>
+        <v>2.399803638458252</v>
       </c>
       <c r="F12" t="n">
-        <v>2.04631233215332</v>
+        <v>2.460898637771606</v>
       </c>
       <c r="G12" t="n">
-        <v>1.99392294883728</v>
+        <v>2.387827634811401</v>
       </c>
       <c r="H12" t="n">
-        <v>2.289189338684082</v>
+        <v>2.318613052368164</v>
       </c>
       <c r="I12" t="n">
-        <v>2.701167583465576</v>
+        <v>2.339531183242798</v>
       </c>
       <c r="J12" t="n">
-        <v>2.376967430114746</v>
+        <v>2.287515163421631</v>
       </c>
       <c r="K12" t="n">
-        <v>2.079239845275879</v>
+        <v>2.424870252609253</v>
       </c>
       <c r="L12" t="n">
-        <v>2.319199538230896</v>
+        <v>2.422969365119934</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>2.236320018768311</v>
+        <v>2.622287034988403</v>
       </c>
       <c r="C13" t="n">
-        <v>2.210007667541504</v>
+        <v>2.548584938049316</v>
       </c>
       <c r="D13" t="n">
-        <v>2.315488338470459</v>
+        <v>2.281468152999878</v>
       </c>
       <c r="E13" t="n">
-        <v>2.351922750473022</v>
+        <v>2.594602346420288</v>
       </c>
       <c r="F13" t="n">
-        <v>2.080988883972168</v>
+        <v>2.433691263198853</v>
       </c>
       <c r="G13" t="n">
-        <v>2.759487867355347</v>
+        <v>2.462085723876953</v>
       </c>
       <c r="H13" t="n">
-        <v>2.315613031387329</v>
+        <v>2.476163864135742</v>
       </c>
       <c r="I13" t="n">
-        <v>2.520101547241211</v>
+        <v>2.627588748931885</v>
       </c>
       <c r="J13" t="n">
-        <v>2.307646036148071</v>
+        <v>2.536790132522583</v>
       </c>
       <c r="K13" t="n">
-        <v>2.255779266357422</v>
+        <v>2.499288082122803</v>
       </c>
       <c r="L13" t="n">
-        <v>2.335335540771484</v>
+        <v>2.50825502872467</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>2.625613451004028</v>
+        <v>2.557039260864258</v>
       </c>
       <c r="C14" t="n">
-        <v>2.366009473800659</v>
+        <v>2.494409799575806</v>
       </c>
       <c r="D14" t="n">
-        <v>2.353527545928955</v>
+        <v>2.367850065231323</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2597496509552</v>
+        <v>2.505780220031738</v>
       </c>
       <c r="F14" t="n">
-        <v>2.138058185577393</v>
+        <v>2.682685613632202</v>
       </c>
       <c r="G14" t="n">
-        <v>2.334022045135498</v>
+        <v>2.45332407951355</v>
       </c>
       <c r="H14" t="n">
-        <v>2.58350944519043</v>
+        <v>2.599213838577271</v>
       </c>
       <c r="I14" t="n">
-        <v>2.108126163482666</v>
+        <v>2.400539398193359</v>
       </c>
       <c r="J14" t="n">
-        <v>2.408881902694702</v>
+        <v>2.505361080169678</v>
       </c>
       <c r="K14" t="n">
-        <v>2.41686224937439</v>
+        <v>2.537604331970215</v>
       </c>
       <c r="L14" t="n">
-        <v>2.359436011314392</v>
+        <v>2.51038076877594</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>2.189920663833618</v>
+        <v>2.289721250534058</v>
       </c>
       <c r="C15" t="n">
-        <v>1.986932277679443</v>
+        <v>2.201725244522095</v>
       </c>
       <c r="D15" t="n">
-        <v>2.129094123840332</v>
+        <v>2.263194799423218</v>
       </c>
       <c r="E15" t="n">
-        <v>2.132591724395752</v>
+        <v>2.195334672927856</v>
       </c>
       <c r="F15" t="n">
-        <v>1.934576511383057</v>
+        <v>2.312538623809814</v>
       </c>
       <c r="G15" t="n">
-        <v>2.336332559585571</v>
+        <v>2.22219705581665</v>
       </c>
       <c r="H15" t="n">
-        <v>2.56450343132019</v>
+        <v>2.267083168029785</v>
       </c>
       <c r="I15" t="n">
-        <v>2.573499441146851</v>
+        <v>2.256767272949219</v>
       </c>
       <c r="J15" t="n">
-        <v>2.474722385406494</v>
+        <v>2.211751699447632</v>
       </c>
       <c r="K15" t="n">
-        <v>2.80190110206604</v>
+        <v>2.331494331359863</v>
       </c>
       <c r="L15" t="n">
-        <v>2.312407422065735</v>
+        <v>2.255180811882019</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>2.531612157821655</v>
+        <v>2.341781616210938</v>
       </c>
       <c r="C16" t="n">
-        <v>2.788994073867798</v>
+        <v>2.402666568756104</v>
       </c>
       <c r="D16" t="n">
-        <v>2.643290042877197</v>
+        <v>2.646044015884399</v>
       </c>
       <c r="E16" t="n">
-        <v>2.963077783584595</v>
+        <v>2.368438959121704</v>
       </c>
       <c r="F16" t="n">
-        <v>2.553545475006104</v>
+        <v>2.67469048500061</v>
       </c>
       <c r="G16" t="n">
-        <v>2.789940595626831</v>
+        <v>2.35402774810791</v>
       </c>
       <c r="H16" t="n">
-        <v>2.446834325790405</v>
+        <v>2.487120628356934</v>
       </c>
       <c r="I16" t="n">
-        <v>2.409912109375</v>
+        <v>2.492763519287109</v>
       </c>
       <c r="J16" t="n">
-        <v>2.200438022613525</v>
+        <v>2.638944864273071</v>
       </c>
       <c r="K16" t="n">
-        <v>2.45626974105835</v>
+        <v>2.408272743225098</v>
       </c>
       <c r="L16" t="n">
-        <v>2.578391432762146</v>
+        <v>2.481475114822388</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>2.50813364982605</v>
+        <v>2.169186115264893</v>
       </c>
       <c r="C17" t="n">
-        <v>2.154006481170654</v>
+        <v>2.428942918777466</v>
       </c>
       <c r="D17" t="n">
-        <v>2.013861656188965</v>
+        <v>2.354022264480591</v>
       </c>
       <c r="E17" t="n">
-        <v>2.005891561508179</v>
+        <v>2.449933290481567</v>
       </c>
       <c r="F17" t="n">
-        <v>2.138558149337769</v>
+        <v>2.496013402938843</v>
       </c>
       <c r="G17" t="n">
-        <v>2.123974800109863</v>
+        <v>2.486943483352661</v>
       </c>
       <c r="H17" t="n">
-        <v>2.056758880615234</v>
+        <v>2.233896732330322</v>
       </c>
       <c r="I17" t="n">
-        <v>2.01937460899353</v>
+        <v>2.425078153610229</v>
       </c>
       <c r="J17" t="n">
-        <v>2.289154052734375</v>
+        <v>2.402057409286499</v>
       </c>
       <c r="K17" t="n">
-        <v>2.044285774230957</v>
+        <v>2.265057563781738</v>
       </c>
       <c r="L17" t="n">
-        <v>2.135399961471558</v>
+        <v>2.371113133430481</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>2.285673379898071</v>
+        <v>2.711048364639282</v>
       </c>
       <c r="C18" t="n">
-        <v>2.251259326934814</v>
+        <v>2.888410568237305</v>
       </c>
       <c r="D18" t="n">
-        <v>2.499622344970703</v>
+        <v>2.502586364746094</v>
       </c>
       <c r="E18" t="n">
-        <v>2.423697710037231</v>
+        <v>2.718980312347412</v>
       </c>
       <c r="F18" t="n">
-        <v>2.419700145721436</v>
+        <v>2.798434257507324</v>
       </c>
       <c r="G18" t="n">
-        <v>2.555368900299072</v>
+        <v>2.491909503936768</v>
       </c>
       <c r="H18" t="n">
-        <v>2.401759147644043</v>
+        <v>2.572006940841675</v>
       </c>
       <c r="I18" t="n">
-        <v>2.275078296661377</v>
+        <v>2.602445363998413</v>
       </c>
       <c r="J18" t="n">
-        <v>2.350884914398193</v>
+        <v>2.727872848510742</v>
       </c>
       <c r="K18" t="n">
-        <v>2.236184120178223</v>
+        <v>2.860958576202393</v>
       </c>
       <c r="L18" t="n">
-        <v>2.369922828674317</v>
+        <v>2.687465310096741</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>2.169377326965332</v>
+        <v>2.398472309112549</v>
       </c>
       <c r="C19" t="n">
-        <v>2.332659959793091</v>
+        <v>2.246745586395264</v>
       </c>
       <c r="D19" t="n">
-        <v>2.030707359313965</v>
+        <v>2.637833595275879</v>
       </c>
       <c r="E19" t="n">
-        <v>2.269642114639282</v>
+        <v>2.373405933380127</v>
       </c>
       <c r="F19" t="n">
-        <v>2.316599130630493</v>
+        <v>2.473634958267212</v>
       </c>
       <c r="G19" t="n">
-        <v>2.133061647415161</v>
+        <v>2.409623861312866</v>
       </c>
       <c r="H19" t="n">
-        <v>2.28071117401123</v>
+        <v>2.31391453742981</v>
       </c>
       <c r="I19" t="n">
-        <v>2.295668601989746</v>
+        <v>2.480102777481079</v>
       </c>
       <c r="J19" t="n">
-        <v>2.151527881622314</v>
+        <v>2.40045428276062</v>
       </c>
       <c r="K19" t="n">
-        <v>2.026827573776245</v>
+        <v>2.405268669128418</v>
       </c>
       <c r="L19" t="n">
-        <v>2.200678277015686</v>
+        <v>2.413945651054382</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>2.274921655654907</v>
+        <v>2.535001516342163</v>
       </c>
       <c r="C20" t="n">
-        <v>2.197888374328613</v>
+        <v>2.306544542312622</v>
       </c>
       <c r="D20" t="n">
-        <v>2.129580497741699</v>
+        <v>2.36120080947876</v>
       </c>
       <c r="E20" t="n">
-        <v>2.161979913711548</v>
+        <v>2.415808439254761</v>
       </c>
       <c r="F20" t="n">
-        <v>2.249789476394653</v>
+        <v>2.498590230941772</v>
       </c>
       <c r="G20" t="n">
-        <v>2.148020505905151</v>
+        <v>2.5482177734375</v>
       </c>
       <c r="H20" t="n">
-        <v>2.132058620452881</v>
+        <v>2.435593843460083</v>
       </c>
       <c r="I20" t="n">
-        <v>2.008882761001587</v>
+        <v>2.480061292648315</v>
       </c>
       <c r="J20" t="n">
-        <v>2.123607397079468</v>
+        <v>2.552239894866943</v>
       </c>
       <c r="K20" t="n">
-        <v>1.971468687057495</v>
+        <v>2.335107564926147</v>
       </c>
       <c r="L20" t="n">
-        <v>2.1398197889328</v>
+        <v>2.446836590766907</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>2.130578279495239</v>
+        <v>2.398464679718018</v>
       </c>
       <c r="C21" t="n">
-        <v>2.037797927856445</v>
+        <v>2.427713871002197</v>
       </c>
       <c r="D21" t="n">
-        <v>2.198391437530518</v>
+        <v>2.35729193687439</v>
       </c>
       <c r="E21" t="n">
-        <v>2.275722503662109</v>
+        <v>2.512579679489136</v>
       </c>
       <c r="F21" t="n">
-        <v>2.190915107727051</v>
+        <v>2.498844146728516</v>
       </c>
       <c r="G21" t="n">
-        <v>2.113113641738892</v>
+        <v>2.563225984573364</v>
       </c>
       <c r="H21" t="n">
-        <v>2.103140592575073</v>
+        <v>2.479530096054077</v>
       </c>
       <c r="I21" t="n">
-        <v>1.998920679092407</v>
+        <v>2.342898845672607</v>
       </c>
       <c r="J21" t="n">
-        <v>2.123594522476196</v>
+        <v>2.511603832244873</v>
       </c>
       <c r="K21" t="n">
-        <v>2.03181529045105</v>
+        <v>2.411863088607788</v>
       </c>
       <c r="L21" t="n">
-        <v>2.120398998260498</v>
+        <v>2.450401616096497</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>2.089196443557739</v>
+        <v>2.25398063659668</v>
       </c>
       <c r="C22" t="n">
-        <v>2.021832227706909</v>
+        <v>2.414176225662231</v>
       </c>
       <c r="D22" t="n">
-        <v>1.998934268951416</v>
+        <v>2.241024017333984</v>
       </c>
       <c r="E22" t="n">
-        <v>2.058748006820679</v>
+        <v>2.195782661437988</v>
       </c>
       <c r="F22" t="n">
-        <v>2.049288272857666</v>
+        <v>2.306196689605713</v>
       </c>
       <c r="G22" t="n">
-        <v>2.219358682632446</v>
+        <v>2.340360164642334</v>
       </c>
       <c r="H22" t="n">
-        <v>2.061732053756714</v>
+        <v>2.332994937896729</v>
       </c>
       <c r="I22" t="n">
-        <v>1.987925291061401</v>
+        <v>2.387074708938599</v>
       </c>
       <c r="J22" t="n">
-        <v>2.004883766174316</v>
+        <v>2.356908559799194</v>
       </c>
       <c r="K22" t="n">
-        <v>2.065248489379883</v>
+        <v>2.381621122360229</v>
       </c>
       <c r="L22" t="n">
-        <v>2.055714750289917</v>
+        <v>2.321011972427368</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>1.858253479003906</v>
+        <v>2.251618146896362</v>
       </c>
       <c r="C23" t="n">
-        <v>1.867765426635742</v>
+        <v>2.141607999801636</v>
       </c>
       <c r="D23" t="n">
-        <v>1.882704019546509</v>
+        <v>2.094411611557007</v>
       </c>
       <c r="E23" t="n">
-        <v>1.743056774139404</v>
+        <v>2.29853081703186</v>
       </c>
       <c r="F23" t="n">
-        <v>1.974978446960449</v>
+        <v>2.180397987365723</v>
       </c>
       <c r="G23" t="n">
-        <v>1.857266187667847</v>
+        <v>2.019949436187744</v>
       </c>
       <c r="H23" t="n">
-        <v>1.874751091003418</v>
+        <v>2.072313785552979</v>
       </c>
       <c r="I23" t="n">
-        <v>1.901663064956665</v>
+        <v>2.09796929359436</v>
       </c>
       <c r="J23" t="n">
-        <v>1.837316036224365</v>
+        <v>2.097336530685425</v>
       </c>
       <c r="K23" t="n">
-        <v>1.807920217514038</v>
+        <v>2.153318881988525</v>
       </c>
       <c r="L23" t="n">
-        <v>1.860567474365234</v>
+        <v>2.140745449066162</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>1.876732349395752</v>
+        <v>2.130715847015381</v>
       </c>
       <c r="C24" t="n">
-        <v>1.899646759033203</v>
+        <v>2.224452257156372</v>
       </c>
       <c r="D24" t="n">
-        <v>1.837323665618896</v>
+        <v>2.204270124435425</v>
       </c>
       <c r="E24" t="n">
-        <v>1.986946821212769</v>
+        <v>2.571280479431152</v>
       </c>
       <c r="F24" t="n">
-        <v>1.927104949951172</v>
+        <v>2.409899950027466</v>
       </c>
       <c r="G24" t="n">
-        <v>1.992413282394409</v>
+        <v>2.266935586929321</v>
       </c>
       <c r="H24" t="n">
-        <v>1.985944032669067</v>
+        <v>2.113224029541016</v>
       </c>
       <c r="I24" t="n">
-        <v>1.838820934295654</v>
+        <v>2.181777000427246</v>
       </c>
       <c r="J24" t="n">
-        <v>1.989419937133789</v>
+        <v>2.219067811965942</v>
       </c>
       <c r="K24" t="n">
-        <v>1.901655435562134</v>
+        <v>2.477369070053101</v>
       </c>
       <c r="L24" t="n">
-        <v>1.923600816726684</v>
+        <v>2.279899215698242</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>2.062243223190308</v>
+        <v>2.368136405944824</v>
       </c>
       <c r="C25" t="n">
-        <v>1.992937088012695</v>
+        <v>2.468755960464478</v>
       </c>
       <c r="D25" t="n">
-        <v>2.000279426574707</v>
+        <v>2.242613077163696</v>
       </c>
       <c r="E25" t="n">
-        <v>2.226211786270142</v>
+        <v>2.458383560180664</v>
       </c>
       <c r="F25" t="n">
-        <v>2.115009069442749</v>
+        <v>2.197515726089478</v>
       </c>
       <c r="G25" t="n">
-        <v>2.500027894973755</v>
+        <v>2.35564661026001</v>
       </c>
       <c r="H25" t="n">
-        <v>2.192208528518677</v>
+        <v>2.404206037521362</v>
       </c>
       <c r="I25" t="n">
-        <v>1.974972248077393</v>
+        <v>2.387253522872925</v>
       </c>
       <c r="J25" t="n">
-        <v>1.924590587615967</v>
+        <v>2.406903982162476</v>
       </c>
       <c r="K25" t="n">
-        <v>2.153015613555908</v>
+        <v>2.436332702636719</v>
       </c>
       <c r="L25" t="n">
-        <v>2.11414954662323</v>
+        <v>2.372574758529663</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>2.112639427185059</v>
+        <v>2.443100214004517</v>
       </c>
       <c r="C26" t="n">
-        <v>2.262231588363647</v>
+        <v>2.571777105331421</v>
       </c>
       <c r="D26" t="n">
-        <v>1.960018634796143</v>
+        <v>2.607894420623779</v>
       </c>
       <c r="E26" t="n">
-        <v>2.246280431747437</v>
+        <v>2.439389228820801</v>
       </c>
       <c r="F26" t="n">
-        <v>2.315608978271484</v>
+        <v>2.717147827148438</v>
       </c>
       <c r="G26" t="n">
-        <v>2.173403024673462</v>
+        <v>2.364188432693481</v>
       </c>
       <c r="H26" t="n">
-        <v>2.466575145721436</v>
+        <v>2.659970045089722</v>
       </c>
       <c r="I26" t="n">
-        <v>2.166950941085815</v>
+        <v>2.431589365005493</v>
       </c>
       <c r="J26" t="n">
-        <v>2.397775411605835</v>
+        <v>2.588292360305786</v>
       </c>
       <c r="K26" t="n">
-        <v>2.274579524993896</v>
+        <v>2.534080982208252</v>
       </c>
       <c r="L26" t="n">
-        <v>2.237606310844421</v>
+        <v>2.535742998123169</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>2.499040603637695</v>
+        <v>2.418393135070801</v>
       </c>
       <c r="C27" t="n">
-        <v>2.166871786117554</v>
+        <v>2.174684047698975</v>
       </c>
       <c r="D27" t="n">
-        <v>2.162392854690552</v>
+        <v>2.486218452453613</v>
       </c>
       <c r="E27" t="n">
-        <v>2.145928144454956</v>
+        <v>2.368565082550049</v>
       </c>
       <c r="F27" t="n">
-        <v>2.159400701522827</v>
+        <v>2.143513679504395</v>
       </c>
       <c r="G27" t="n">
-        <v>1.986834764480591</v>
+        <v>2.279603242874146</v>
       </c>
       <c r="H27" t="n">
-        <v>1.976349830627441</v>
+        <v>2.19976544380188</v>
       </c>
       <c r="I27" t="n">
-        <v>1.975858211517334</v>
+        <v>2.420608997344971</v>
       </c>
       <c r="J27" t="n">
-        <v>2.029715776443481</v>
+        <v>2.342000722885132</v>
       </c>
       <c r="K27" t="n">
-        <v>2.038760423660278</v>
+        <v>2.419317007064819</v>
       </c>
       <c r="L27" t="n">
-        <v>2.114115309715271</v>
+        <v>2.325266981124878</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>2.102156639099121</v>
+        <v>2.241744995117188</v>
       </c>
       <c r="C28" t="n">
-        <v>2.029829978942871</v>
+        <v>2.218421936035156</v>
       </c>
       <c r="D28" t="n">
-        <v>2.030821800231934</v>
+        <v>2.22284984588623</v>
       </c>
       <c r="E28" t="n">
-        <v>2.21538782119751</v>
+        <v>2.328891515731812</v>
       </c>
       <c r="F28" t="n">
-        <v>2.137562274932861</v>
+        <v>2.240104198455811</v>
       </c>
       <c r="G28" t="n">
-        <v>1.921598434448242</v>
+        <v>2.147470712661743</v>
       </c>
       <c r="H28" t="n">
-        <v>1.869568824768066</v>
+        <v>2.186074733734131</v>
       </c>
       <c r="I28" t="n">
-        <v>1.948957443237305</v>
+        <v>2.476361036300659</v>
       </c>
       <c r="J28" t="n">
-        <v>2.196285486221313</v>
+        <v>2.346279144287109</v>
       </c>
       <c r="K28" t="n">
-        <v>1.996804237365723</v>
+        <v>2.286145210266113</v>
       </c>
       <c r="L28" t="n">
-        <v>2.044897294044495</v>
+        <v>2.269434332847595</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>1.943434715270996</v>
+        <v>2.217346668243408</v>
       </c>
       <c r="C29" t="n">
-        <v>1.944450378417969</v>
+        <v>2.224037885665894</v>
       </c>
       <c r="D29" t="n">
-        <v>1.923089981079102</v>
+        <v>2.238146066665649</v>
       </c>
       <c r="E29" t="n">
-        <v>2.078701496124268</v>
+        <v>2.500750064849854</v>
       </c>
       <c r="F29" t="n">
-        <v>2.007893323898315</v>
+        <v>2.327811479568481</v>
       </c>
       <c r="G29" t="n">
-        <v>1.999905109405518</v>
+        <v>2.164848804473877</v>
       </c>
       <c r="H29" t="n">
-        <v>1.953059911727905</v>
+        <v>2.188107252120972</v>
       </c>
       <c r="I29" t="n">
-        <v>2.114113807678223</v>
+        <v>2.301876306533813</v>
       </c>
       <c r="J29" t="n">
-        <v>1.993920803070068</v>
+        <v>2.284172058105469</v>
       </c>
       <c r="K29" t="n">
-        <v>1.989038944244385</v>
+        <v>2.250870227813721</v>
       </c>
       <c r="L29" t="n">
-        <v>1.994760847091675</v>
+        <v>2.269796681404114</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>2.290549755096436</v>
+        <v>2.370229244232178</v>
       </c>
       <c r="C30" t="n">
-        <v>2.157890796661377</v>
+        <v>2.363803386688232</v>
       </c>
       <c r="D30" t="n">
-        <v>2.080085039138794</v>
+        <v>2.313940286636353</v>
       </c>
       <c r="E30" t="n">
-        <v>2.076106071472168</v>
+        <v>2.792592525482178</v>
       </c>
       <c r="F30" t="n">
-        <v>2.01874041557312</v>
+        <v>2.356695890426636</v>
       </c>
       <c r="G30" t="n">
-        <v>2.170843839645386</v>
+        <v>2.382364749908447</v>
       </c>
       <c r="H30" t="n">
-        <v>2.24173378944397</v>
+        <v>2.472383975982666</v>
       </c>
       <c r="I30" t="n">
-        <v>2.272083520889282</v>
+        <v>2.495289087295532</v>
       </c>
       <c r="J30" t="n">
-        <v>1.99978494644165</v>
+        <v>2.55056095123291</v>
       </c>
       <c r="K30" t="n">
-        <v>2.038464069366455</v>
+        <v>2.28035569190979</v>
       </c>
       <c r="L30" t="n">
-        <v>2.134628224372864</v>
+        <v>2.437821578979492</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>1.796325445175171</v>
+        <v>2.021640300750732</v>
       </c>
       <c r="C31" t="n">
-        <v>1.892236709594727</v>
+        <v>2.087161540985107</v>
       </c>
       <c r="D31" t="n">
-        <v>1.828359365463257</v>
+        <v>1.949742794036865</v>
       </c>
       <c r="E31" t="n">
-        <v>2.062746047973633</v>
+        <v>2.05551552772522</v>
       </c>
       <c r="F31" t="n">
-        <v>1.716619253158569</v>
+        <v>1.999655485153198</v>
       </c>
       <c r="G31" t="n">
-        <v>1.787934541702271</v>
+        <v>2.07857871055603</v>
       </c>
       <c r="H31" t="n">
-        <v>1.66825008392334</v>
+        <v>2.144142627716064</v>
       </c>
       <c r="I31" t="n">
-        <v>1.764506578445435</v>
+        <v>1.99282169342041</v>
       </c>
       <c r="J31" t="n">
-        <v>1.924519777297974</v>
+        <v>1.873605489730835</v>
       </c>
       <c r="K31" t="n">
-        <v>1.860256195068359</v>
+        <v>2.131712675094604</v>
       </c>
       <c r="L31" t="n">
-        <v>1.830175399780273</v>
+        <v>2.033457684516907</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>1.922616243362427</v>
+        <v>2.295874834060669</v>
       </c>
       <c r="C32" t="n">
-        <v>2.025370121002197</v>
+        <v>2.111676931381226</v>
       </c>
       <c r="D32" t="n">
-        <v>1.876207113265991</v>
+        <v>2.14161205291748</v>
       </c>
       <c r="E32" t="n">
-        <v>1.8577721118927</v>
+        <v>2.186966896057129</v>
       </c>
       <c r="F32" t="n">
-        <v>1.881706237792969</v>
+        <v>2.103440046310425</v>
       </c>
       <c r="G32" t="n">
-        <v>1.888044118881226</v>
+        <v>2.089154481887817</v>
       </c>
       <c r="H32" t="n">
-        <v>1.919502735137939</v>
+        <v>2.127511739730835</v>
       </c>
       <c r="I32" t="n">
-        <v>1.935465574264526</v>
+        <v>2.346900463104248</v>
       </c>
       <c r="J32" t="n">
-        <v>1.835224866867065</v>
+        <v>2.541030168533325</v>
       </c>
       <c r="K32" t="n">
-        <v>1.906546115875244</v>
+        <v>2.122509479522705</v>
       </c>
       <c r="L32" t="n">
-        <v>1.904845523834229</v>
+        <v>2.206667709350586</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>2.24479079246521</v>
+        <v>2.32048225402832</v>
       </c>
       <c r="C33" t="n">
-        <v>1.917620420455933</v>
+        <v>2.166184425354004</v>
       </c>
       <c r="D33" t="n">
-        <v>2.238287687301636</v>
+        <v>2.214393854141235</v>
       </c>
       <c r="E33" t="n">
-        <v>2.126540899276733</v>
+        <v>2.296888589859009</v>
       </c>
       <c r="F33" t="n">
-        <v>2.143556594848633</v>
+        <v>2.513496398925781</v>
       </c>
       <c r="G33" t="n">
-        <v>2.237800359725952</v>
+        <v>2.419087886810303</v>
       </c>
       <c r="H33" t="n">
-        <v>2.142936706542969</v>
+        <v>2.567026853561401</v>
       </c>
       <c r="I33" t="n">
-        <v>2.120489597320557</v>
+        <v>2.256451845169067</v>
       </c>
       <c r="J33" t="n">
-        <v>1.924883604049683</v>
+        <v>2.384748697280884</v>
       </c>
       <c r="K33" t="n">
-        <v>2.264244556427002</v>
+        <v>2.39059042930603</v>
       </c>
       <c r="L33" t="n">
-        <v>2.13611512184143</v>
+        <v>2.352935123443603</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>1.976978063583374</v>
+        <v>1.986411094665527</v>
       </c>
       <c r="C34" t="n">
-        <v>1.988937854766846</v>
+        <v>1.993735551834106</v>
       </c>
       <c r="D34" t="n">
-        <v>1.964013338088989</v>
+        <v>2.13013744354248</v>
       </c>
       <c r="E34" t="n">
-        <v>1.947544813156128</v>
+        <v>2.347424507141113</v>
       </c>
       <c r="F34" t="n">
-        <v>1.948890686035156</v>
+        <v>2.090676069259644</v>
       </c>
       <c r="G34" t="n">
-        <v>1.996302127838135</v>
+        <v>1.994431018829346</v>
       </c>
       <c r="H34" t="n">
-        <v>1.891575336456299</v>
+        <v>2.030952930450439</v>
       </c>
       <c r="I34" t="n">
-        <v>1.896587610244751</v>
+        <v>2.266604900360107</v>
       </c>
       <c r="J34" t="n">
-        <v>2.095065593719482</v>
+        <v>2.144231796264648</v>
       </c>
       <c r="K34" t="n">
-        <v>1.942961454391479</v>
+        <v>2.005796670913696</v>
       </c>
       <c r="L34" t="n">
-        <v>1.964885687828064</v>
+        <v>2.099040198326111</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>2.431708574295044</v>
+        <v>2.588626623153687</v>
       </c>
       <c r="C35" t="n">
-        <v>2.316485643386841</v>
+        <v>2.398677110671997</v>
       </c>
       <c r="D35" t="n">
-        <v>2.65610408782959</v>
+        <v>2.439778804779053</v>
       </c>
       <c r="E35" t="n">
-        <v>2.501019716262817</v>
+        <v>2.692342042922974</v>
       </c>
       <c r="F35" t="n">
-        <v>2.432187080383301</v>
+        <v>2.610947132110596</v>
       </c>
       <c r="G35" t="n">
-        <v>2.586809873580933</v>
+        <v>2.536339282989502</v>
       </c>
       <c r="H35" t="n">
-        <v>2.388813018798828</v>
+        <v>2.57728385925293</v>
       </c>
       <c r="I35" t="n">
-        <v>2.481055736541748</v>
+        <v>2.424444437026978</v>
       </c>
       <c r="J35" t="n">
-        <v>2.14691948890686</v>
+        <v>2.581326007843018</v>
       </c>
       <c r="K35" t="n">
-        <v>2.325951337814331</v>
+        <v>2.743163585662842</v>
       </c>
       <c r="L35" t="n">
-        <v>2.426705455780029</v>
+        <v>2.559292888641358</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>1.896568775177002</v>
+        <v>2.109135389328003</v>
       </c>
       <c r="C36" t="n">
-        <v>2.031716108322144</v>
+        <v>2.129315376281738</v>
       </c>
       <c r="D36" t="n">
-        <v>1.915517330169678</v>
+        <v>2.124330282211304</v>
       </c>
       <c r="E36" t="n">
-        <v>1.972885847091675</v>
+        <v>2.291089534759521</v>
       </c>
       <c r="F36" t="n">
-        <v>1.953449964523315</v>
+        <v>2.102142810821533</v>
       </c>
       <c r="G36" t="n">
-        <v>1.958908319473267</v>
+        <v>2.093583345413208</v>
       </c>
       <c r="H36" t="n">
-        <v>2.064623832702637</v>
+        <v>2.068827152252197</v>
       </c>
       <c r="I36" t="n">
-        <v>1.948940515518188</v>
+        <v>2.176998853683472</v>
       </c>
       <c r="J36" t="n">
-        <v>1.976363182067871</v>
+        <v>2.163125991821289</v>
       </c>
       <c r="K36" t="n">
-        <v>1.813781976699829</v>
+        <v>2.149924039840698</v>
       </c>
       <c r="L36" t="n">
-        <v>1.95327558517456</v>
+        <v>2.140847277641297</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>2.038692235946655</v>
+        <v>2.477752923965454</v>
       </c>
       <c r="C37" t="n">
-        <v>2.244168996810913</v>
+        <v>2.36866569519043</v>
       </c>
       <c r="D37" t="n">
-        <v>2.284141302108765</v>
+        <v>2.402322769165039</v>
       </c>
       <c r="E37" t="n">
-        <v>2.050296545028687</v>
+        <v>2.630961418151855</v>
       </c>
       <c r="F37" t="n">
-        <v>2.084702491760254</v>
+        <v>2.482037305831909</v>
       </c>
       <c r="G37" t="n">
-        <v>2.256747961044312</v>
+        <v>2.374554872512817</v>
       </c>
       <c r="H37" t="n">
-        <v>2.131087303161621</v>
+        <v>2.559231042861938</v>
       </c>
       <c r="I37" t="n">
-        <v>2.162478685379028</v>
+        <v>2.303199291229248</v>
       </c>
       <c r="J37" t="n">
-        <v>1.948529481887817</v>
+        <v>2.45014214515686</v>
       </c>
       <c r="K37" t="n">
-        <v>2.0098717212677</v>
+        <v>2.489206552505493</v>
       </c>
       <c r="L37" t="n">
-        <v>2.121071672439575</v>
+        <v>2.453807401657104</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>2.352017879486084</v>
+        <v>2.662497997283936</v>
       </c>
       <c r="C38" t="n">
-        <v>2.384418249130249</v>
+        <v>2.590911626815796</v>
       </c>
       <c r="D38" t="n">
-        <v>2.392926692962646</v>
+        <v>2.725078105926514</v>
       </c>
       <c r="E38" t="n">
-        <v>2.310611724853516</v>
+        <v>2.909618616104126</v>
       </c>
       <c r="F38" t="n">
-        <v>2.324574947357178</v>
+        <v>2.570711135864258</v>
       </c>
       <c r="G38" t="n">
-        <v>2.366969585418701</v>
+        <v>2.640556573867798</v>
       </c>
       <c r="H38" t="n">
-        <v>2.535037279129028</v>
+        <v>2.510007619857788</v>
       </c>
       <c r="I38" t="n">
-        <v>2.236821889877319</v>
+        <v>2.574727773666382</v>
       </c>
       <c r="J38" t="n">
-        <v>2.38893723487854</v>
+        <v>2.522582769393921</v>
       </c>
       <c r="K38" t="n">
-        <v>2.514089584350586</v>
+        <v>2.65104341506958</v>
       </c>
       <c r="L38" t="n">
-        <v>2.380640506744385</v>
+        <v>2.63577356338501</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>2.063726663589478</v>
+        <v>2.452512979507446</v>
       </c>
       <c r="C39" t="n">
-        <v>2.400895357131958</v>
+        <v>2.542837142944336</v>
       </c>
       <c r="D39" t="n">
-        <v>2.1320641040802</v>
+        <v>2.595187664031982</v>
       </c>
       <c r="E39" t="n">
-        <v>1.955012083053589</v>
+        <v>2.296799421310425</v>
       </c>
       <c r="F39" t="n">
-        <v>2.038793802261353</v>
+        <v>2.361916065216064</v>
       </c>
       <c r="G39" t="n">
-        <v>2.061253309249878</v>
+        <v>2.523006916046143</v>
       </c>
       <c r="H39" t="n">
-        <v>2.30262565612793</v>
+        <v>2.667106628417969</v>
       </c>
       <c r="I39" t="n">
-        <v>2.150020122528076</v>
+        <v>2.325423002243042</v>
       </c>
       <c r="J39" t="n">
-        <v>2.202397584915161</v>
+        <v>2.518842697143555</v>
       </c>
       <c r="K39" t="n">
-        <v>2.05626654624939</v>
+        <v>2.326310873031616</v>
       </c>
       <c r="L39" t="n">
-        <v>2.136305522918701</v>
+        <v>2.460994338989258</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>2.015864133834839</v>
+        <v>2.250782012939453</v>
       </c>
       <c r="C40" t="n">
-        <v>1.92756986618042</v>
+        <v>2.208143711090088</v>
       </c>
       <c r="D40" t="n">
-        <v>2.081197500228882</v>
+        <v>2.276464700698853</v>
       </c>
       <c r="E40" t="n">
-        <v>1.950520277023315</v>
+        <v>2.293222904205322</v>
       </c>
       <c r="F40" t="n">
-        <v>1.962997198104858</v>
+        <v>2.300800085067749</v>
       </c>
       <c r="G40" t="n">
-        <v>2.139045000076294</v>
+        <v>2.25506067276001</v>
       </c>
       <c r="H40" t="n">
-        <v>1.967987775802612</v>
+        <v>2.116522312164307</v>
       </c>
       <c r="I40" t="n">
-        <v>1.991918563842773</v>
+        <v>2.214130878448486</v>
       </c>
       <c r="J40" t="n">
-        <v>1.994924306869507</v>
+        <v>2.178125619888306</v>
       </c>
       <c r="K40" t="n">
-        <v>2.010872840881348</v>
+        <v>2.195845603942871</v>
       </c>
       <c r="L40" t="n">
-        <v>2.004289746284485</v>
+        <v>2.228909850120544</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>2.199398517608643</v>
+        <v>2.466490268707275</v>
       </c>
       <c r="C41" t="n">
-        <v>2.164970397949219</v>
+        <v>2.751783609390259</v>
       </c>
       <c r="D41" t="n">
-        <v>2.271730422973633</v>
+        <v>2.470931529998779</v>
       </c>
       <c r="E41" t="n">
-        <v>2.222338914871216</v>
+        <v>2.509487152099609</v>
       </c>
       <c r="F41" t="n">
-        <v>2.198398351669312</v>
+        <v>2.539731502532959</v>
       </c>
       <c r="G41" t="n">
-        <v>2.186448097229004</v>
+        <v>2.474338531494141</v>
       </c>
       <c r="H41" t="n">
-        <v>2.379947900772095</v>
+        <v>2.507763624191284</v>
       </c>
       <c r="I41" t="n">
-        <v>2.161995649337769</v>
+        <v>2.653799533843994</v>
       </c>
       <c r="J41" t="n">
-        <v>2.269725799560547</v>
+        <v>2.506205081939697</v>
       </c>
       <c r="K41" t="n">
-        <v>2.139062166213989</v>
+        <v>2.453626871109009</v>
       </c>
       <c r="L41" t="n">
-        <v>2.219401621818542</v>
+        <v>2.533415770530701</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>1.948077440261841</v>
+        <v>2.173384666442871</v>
       </c>
       <c r="C42" t="n">
-        <v>1.854262828826904</v>
+        <v>2.263017892837524</v>
       </c>
       <c r="D42" t="n">
-        <v>1.840308427810669</v>
+        <v>2.160875082015991</v>
       </c>
       <c r="E42" t="n">
-        <v>1.970978498458862</v>
+        <v>2.174541234970093</v>
       </c>
       <c r="F42" t="n">
-        <v>1.874723434448242</v>
+        <v>2.292347431182861</v>
       </c>
       <c r="G42" t="n">
-        <v>2.164987564086914</v>
+        <v>2.362668752670288</v>
       </c>
       <c r="H42" t="n">
-        <v>1.925102233886719</v>
+        <v>2.211710691452026</v>
       </c>
       <c r="I42" t="n">
-        <v>2.059775590896606</v>
+        <v>2.063000917434692</v>
       </c>
       <c r="J42" t="n">
-        <v>1.962008476257324</v>
+        <v>2.286922693252563</v>
       </c>
       <c r="K42" t="n">
-        <v>1.933573246002197</v>
+        <v>2.111459016799927</v>
       </c>
       <c r="L42" t="n">
-        <v>1.953379774093628</v>
+        <v>2.209992837905884</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>2.101148366928101</v>
+        <v>2.458339929580688</v>
       </c>
       <c r="C43" t="n">
-        <v>2.252288103103638</v>
+        <v>2.570556163787842</v>
       </c>
       <c r="D43" t="n">
-        <v>1.952024936676025</v>
+        <v>2.248333692550659</v>
       </c>
       <c r="E43" t="n">
-        <v>2.240326404571533</v>
+        <v>2.438768148422241</v>
       </c>
       <c r="F43" t="n">
-        <v>2.13644552230835</v>
+        <v>2.306734085083008</v>
       </c>
       <c r="G43" t="n">
-        <v>2.183814525604248</v>
+        <v>2.443285942077637</v>
       </c>
       <c r="H43" t="n">
-        <v>2.063155651092529</v>
+        <v>2.6187744140625</v>
       </c>
       <c r="I43" t="n">
-        <v>2.098071575164795</v>
+        <v>2.383482456207275</v>
       </c>
       <c r="J43" t="n">
-        <v>1.997795343399048</v>
+        <v>2.388962745666504</v>
       </c>
       <c r="K43" t="n">
-        <v>2.053668022155762</v>
+        <v>2.124336242675781</v>
       </c>
       <c r="L43" t="n">
-        <v>2.107873845100403</v>
+        <v>2.398157382011413</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>2.110015630722046</v>
+        <v>2.268196582794189</v>
       </c>
       <c r="C44" t="n">
-        <v>1.898558378219604</v>
+        <v>2.31519603729248</v>
       </c>
       <c r="D44" t="n">
-        <v>2.008796215057373</v>
+        <v>2.401761293411255</v>
       </c>
       <c r="E44" t="n">
-        <v>1.951926469802856</v>
+        <v>2.294624805450439</v>
       </c>
       <c r="F44" t="n">
-        <v>1.883588314056396</v>
+        <v>2.194501638412476</v>
       </c>
       <c r="G44" t="n">
-        <v>1.963397264480591</v>
+        <v>2.294452905654907</v>
       </c>
       <c r="H44" t="n">
-        <v>2.014467477798462</v>
+        <v>2.194467782974243</v>
       </c>
       <c r="I44" t="n">
-        <v>2.061169862747192</v>
+        <v>2.377766370773315</v>
       </c>
       <c r="J44" t="n">
-        <v>1.97087025642395</v>
+        <v>2.27358341217041</v>
       </c>
       <c r="K44" t="n">
-        <v>1.927482128143311</v>
+        <v>2.100366353988647</v>
       </c>
       <c r="L44" t="n">
-        <v>1.979027199745178</v>
+        <v>2.271491718292237</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>2.194299459457397</v>
+        <v>2.134752511978149</v>
       </c>
       <c r="C45" t="n">
-        <v>1.954422473907471</v>
+        <v>2.153661012649536</v>
       </c>
       <c r="D45" t="n">
-        <v>1.98383355140686</v>
+        <v>2.210926532745361</v>
       </c>
       <c r="E45" t="n">
-        <v>2.080087423324585</v>
+        <v>2.233297109603882</v>
       </c>
       <c r="F45" t="n">
-        <v>1.840208530426025</v>
+        <v>2.051118612289429</v>
       </c>
       <c r="G45" t="n">
-        <v>1.989360570907593</v>
+        <v>2.131309747695923</v>
       </c>
       <c r="H45" t="n">
-        <v>2.895220279693604</v>
+        <v>2.066204071044922</v>
       </c>
       <c r="I45" t="n">
-        <v>2.257280588150024</v>
+        <v>2.281778812408447</v>
       </c>
       <c r="J45" t="n">
-        <v>2.111133813858032</v>
+        <v>2.074364423751831</v>
       </c>
       <c r="K45" t="n">
-        <v>1.84181809425354</v>
+        <v>2.073250532150269</v>
       </c>
       <c r="L45" t="n">
-        <v>2.114766478538513</v>
+        <v>2.141066336631775</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>2.030463695526123</v>
+        <v>2.052064418792725</v>
       </c>
       <c r="C46" t="n">
-        <v>2.136941909790039</v>
+        <v>2.113236904144287</v>
       </c>
       <c r="D46" t="n">
-        <v>1.941978454589844</v>
+        <v>2.023625373840332</v>
       </c>
       <c r="E46" t="n">
-        <v>1.890600204467773</v>
+        <v>2.048534870147705</v>
       </c>
       <c r="F46" t="n">
-        <v>1.806314468383789</v>
+        <v>2.162185192108154</v>
       </c>
       <c r="G46" t="n">
-        <v>1.696085214614868</v>
+        <v>2.122604131698608</v>
       </c>
       <c r="H46" t="n">
-        <v>2.234431743621826</v>
+        <v>2.076261043548584</v>
       </c>
       <c r="I46" t="n">
-        <v>2.209262371063232</v>
+        <v>1.965737104415894</v>
       </c>
       <c r="J46" t="n">
-        <v>2.065139055252075</v>
+        <v>2.053086757659912</v>
       </c>
       <c r="K46" t="n">
-        <v>1.888083219528198</v>
+        <v>2.098341941833496</v>
       </c>
       <c r="L46" t="n">
-        <v>1.989930033683777</v>
+        <v>2.07156777381897</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>2.424566268920898</v>
+        <v>2.891137599945068</v>
       </c>
       <c r="C47" t="n">
-        <v>2.556977987289429</v>
+        <v>2.712094068527222</v>
       </c>
       <c r="D47" t="n">
-        <v>2.572471380233765</v>
+        <v>2.717012643814087</v>
       </c>
       <c r="E47" t="n">
-        <v>2.709613800048828</v>
+        <v>3.089044570922852</v>
       </c>
       <c r="F47" t="n">
-        <v>2.586425542831421</v>
+        <v>3.030603647232056</v>
       </c>
       <c r="G47" t="n">
-        <v>2.462754726409912</v>
+        <v>2.705987691879272</v>
       </c>
       <c r="H47" t="n">
-        <v>2.506123065948486</v>
+        <v>2.741621017456055</v>
       </c>
       <c r="I47" t="n">
-        <v>2.555490970611572</v>
+        <v>2.683212041854858</v>
       </c>
       <c r="J47" t="n">
-        <v>3.106660604476929</v>
+        <v>2.774292707443237</v>
       </c>
       <c r="K47" t="n">
-        <v>2.716593742370605</v>
+        <v>2.909453630447388</v>
       </c>
       <c r="L47" t="n">
-        <v>2.619767808914184</v>
+        <v>2.82544596195221</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>2.26523756980896</v>
+        <v>2.315899133682251</v>
       </c>
       <c r="C48" t="n">
-        <v>2.130584478378296</v>
+        <v>2.357062339782715</v>
       </c>
       <c r="D48" t="n">
-        <v>2.534085035324097</v>
+        <v>2.347320079803467</v>
       </c>
       <c r="E48" t="n">
-        <v>2.262772083282471</v>
+        <v>2.521454095840454</v>
       </c>
       <c r="F48" t="n">
-        <v>2.135054588317871</v>
+        <v>2.36581015586853</v>
       </c>
       <c r="G48" t="n">
-        <v>2.141059160232544</v>
+        <v>2.481377840042114</v>
       </c>
       <c r="H48" t="n">
-        <v>2.329574346542358</v>
+        <v>2.437445640563965</v>
       </c>
       <c r="I48" t="n">
-        <v>2.189426422119141</v>
+        <v>2.343564033508301</v>
       </c>
       <c r="J48" t="n">
-        <v>2.356010913848877</v>
+        <v>2.342345476150513</v>
       </c>
       <c r="K48" t="n">
-        <v>2.320621490478516</v>
+        <v>2.430480480194092</v>
       </c>
       <c r="L48" t="n">
-        <v>2.266442608833313</v>
+        <v>2.39427592754364</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>2.235310554504395</v>
+        <v>2.577511787414551</v>
       </c>
       <c r="C49" t="n">
-        <v>2.302640914916992</v>
+        <v>2.627426385879517</v>
       </c>
       <c r="D49" t="n">
-        <v>2.293663024902344</v>
+        <v>2.614540576934814</v>
       </c>
       <c r="E49" t="n">
-        <v>2.438310861587524</v>
+        <v>2.463959455490112</v>
       </c>
       <c r="F49" t="n">
-        <v>2.714743137359619</v>
+        <v>2.542992353439331</v>
       </c>
       <c r="G49" t="n">
-        <v>2.588290691375732</v>
+        <v>2.484755516052246</v>
       </c>
       <c r="H49" t="n">
-        <v>2.591761112213135</v>
+        <v>2.501424074172974</v>
       </c>
       <c r="I49" t="n">
-        <v>2.997255563735962</v>
+        <v>2.773495435714722</v>
       </c>
       <c r="J49" t="n">
-        <v>2.797726392745972</v>
+        <v>2.537809133529663</v>
       </c>
       <c r="K49" t="n">
-        <v>2.598245620727539</v>
+        <v>2.460055589675903</v>
       </c>
       <c r="L49" t="n">
-        <v>2.555794787406922</v>
+        <v>2.558397030830383</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>2.150396108627319</v>
+        <v>2.062027931213379</v>
       </c>
       <c r="C50" t="n">
-        <v>2.211543798446655</v>
+        <v>2.273791313171387</v>
       </c>
       <c r="D50" t="n">
-        <v>2.246151924133301</v>
+        <v>2.211583137512207</v>
       </c>
       <c r="E50" t="n">
-        <v>2.518354892730713</v>
+        <v>2.457578420639038</v>
       </c>
       <c r="F50" t="n">
-        <v>2.252769947052002</v>
+        <v>2.255273103713989</v>
       </c>
       <c r="G50" t="n">
-        <v>2.164967775344849</v>
+        <v>2.186841487884521</v>
       </c>
       <c r="H50" t="n">
-        <v>2.439304351806641</v>
+        <v>2.249320507049561</v>
       </c>
       <c r="I50" t="n">
-        <v>2.304027080535889</v>
+        <v>2.279580593109131</v>
       </c>
       <c r="J50" t="n">
-        <v>2.372467517852783</v>
+        <v>2.349320888519287</v>
       </c>
       <c r="K50" t="n">
-        <v>2.093162775039673</v>
+        <v>2.352019786834717</v>
       </c>
       <c r="L50" t="n">
-        <v>2.275314617156982</v>
+        <v>2.267733716964722</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>2.043319463729858</v>
+        <v>2.213155269622803</v>
       </c>
       <c r="C51" t="n">
-        <v>2.021845579147339</v>
+        <v>2.250005006790161</v>
       </c>
       <c r="D51" t="n">
-        <v>2.194034814834595</v>
+        <v>2.063655376434326</v>
       </c>
       <c r="E51" t="n">
-        <v>2.137948751449585</v>
+        <v>2.197766780853271</v>
       </c>
       <c r="F51" t="n">
-        <v>2.024734735488892</v>
+        <v>2.119079828262329</v>
       </c>
       <c r="G51" t="n">
-        <v>2.043182849884033</v>
+        <v>2.246590614318848</v>
       </c>
       <c r="H51" t="n">
-        <v>1.959389686584473</v>
+        <v>2.213405609130859</v>
       </c>
       <c r="I51" t="n">
-        <v>2.147412538528442</v>
+        <v>2.124918222427368</v>
       </c>
       <c r="J51" t="n">
-        <v>2.035700082778931</v>
+        <v>2.285421133041382</v>
       </c>
       <c r="K51" t="n">
-        <v>2.081081867218018</v>
+        <v>2.272655010223389</v>
       </c>
       <c r="L51" t="n">
-        <v>2.068865036964417</v>
+        <v>2.198665285110474</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.182797064781189</v>
+        <v>2.33855251789093</v>
       </c>
       <c r="C52" t="n">
-        <v>2.185093564987183</v>
+        <v>2.360681014060974</v>
       </c>
       <c r="D52" t="n">
-        <v>2.167919611930847</v>
+        <v>2.331909017562866</v>
       </c>
       <c r="E52" t="n">
-        <v>2.199372034072876</v>
+        <v>2.406134119033814</v>
       </c>
       <c r="F52" t="n">
-        <v>2.156221055984497</v>
+        <v>2.369960536956787</v>
       </c>
       <c r="G52" t="n">
-        <v>2.229514927864075</v>
+        <v>2.343040103912354</v>
       </c>
       <c r="H52" t="n">
-        <v>2.246856722831726</v>
+        <v>2.353103575706482</v>
       </c>
       <c r="I52" t="n">
-        <v>2.23159469127655</v>
+        <v>2.356964802742004</v>
       </c>
       <c r="J52" t="n">
-        <v>2.194881825447082</v>
+        <v>2.380643424987793</v>
       </c>
       <c r="K52" t="n">
-        <v>2.141807713508606</v>
+        <v>2.390960335731506</v>
       </c>
       <c r="L52" t="n">
-        <v>2.193605921268463</v>
+        <v>2.363194944858551</v>
       </c>
     </row>
   </sheetData>
